--- a/data/nzd0455/nzd0455.xlsx
+++ b/data/nzd0455/nzd0455.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W368"/>
+  <dimension ref="A1:W369"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -28048,6 +28048,81 @@
         <v>354.85</v>
       </c>
       <c r="W368" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="369">
+      <c r="A369" s="1" t="inlineStr">
+        <is>
+          <t>2025-11-27 22:26:51+00:00</t>
+        </is>
+      </c>
+      <c r="B369" t="n">
+        <v>383.67</v>
+      </c>
+      <c r="C369" t="n">
+        <v>348.53</v>
+      </c>
+      <c r="D369" t="n">
+        <v>346.18</v>
+      </c>
+      <c r="E369" t="n">
+        <v>357.44</v>
+      </c>
+      <c r="F369" t="n">
+        <v>367.36</v>
+      </c>
+      <c r="G369" t="n">
+        <v>371.8</v>
+      </c>
+      <c r="H369" t="n">
+        <v>368.42</v>
+      </c>
+      <c r="I369" t="n">
+        <v>365.28</v>
+      </c>
+      <c r="J369" t="n">
+        <v>365.35</v>
+      </c>
+      <c r="K369" t="n">
+        <v>366.37</v>
+      </c>
+      <c r="L369" t="n">
+        <v>362.68</v>
+      </c>
+      <c r="M369" t="n">
+        <v>358.94</v>
+      </c>
+      <c r="N369" t="n">
+        <v>355.88</v>
+      </c>
+      <c r="O369" t="n">
+        <v>356.51</v>
+      </c>
+      <c r="P369" t="n">
+        <v>352.74</v>
+      </c>
+      <c r="Q369" t="n">
+        <v>351.21</v>
+      </c>
+      <c r="R369" t="n">
+        <v>351</v>
+      </c>
+      <c r="S369" t="n">
+        <v>345.97</v>
+      </c>
+      <c r="T369" t="n">
+        <v>348.46</v>
+      </c>
+      <c r="U369" t="n">
+        <v>356.61</v>
+      </c>
+      <c r="V369" t="n">
+        <v>352.34</v>
+      </c>
+      <c r="W369" t="inlineStr">
         <is>
           <t>L8</t>
         </is>
@@ -28064,7 +28139,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B380"/>
+  <dimension ref="A1:B381"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -31867,6 +31942,16 @@
       </c>
       <c r="B380" t="n">
         <v>-0.67</v>
+      </c>
+    </row>
+    <row r="381">
+      <c r="A381" t="inlineStr">
+        <is>
+          <t>2025-11-27 22:30:00+00:00</t>
+        </is>
+      </c>
+      <c r="B381" t="n">
+        <v>-0.6</v>
       </c>
     </row>
   </sheetData>
@@ -32035,28 +32120,28 @@
         <v>0.0326</v>
       </c>
       <c r="I2" t="n">
-        <v>0.2565192547597656</v>
+        <v>0.2563128187452734</v>
       </c>
       <c r="J2" t="n">
+        <v>368</v>
+      </c>
+      <c r="K2" t="n">
         <v>367</v>
       </c>
-      <c r="K2" t="n">
-        <v>366</v>
-      </c>
       <c r="L2" t="n">
-        <v>0.02788786173671176</v>
+        <v>0.02799525004571901</v>
       </c>
       <c r="M2" t="n">
-        <v>7.901557878414859</v>
+        <v>7.881212268032868</v>
       </c>
       <c r="N2" t="n">
-        <v>120.7677964247913</v>
+        <v>120.4391319096421</v>
       </c>
       <c r="O2" t="n">
-        <v>10.98944022345048</v>
+        <v>10.97447638430381</v>
       </c>
       <c r="P2" t="n">
-        <v>377.3083931290759</v>
+        <v>377.3106328771697</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -32113,28 +32198,28 @@
         <v>0.08740000000000001</v>
       </c>
       <c r="I3" t="n">
-        <v>0.4767994022738409</v>
+        <v>0.4739970520647219</v>
       </c>
       <c r="J3" t="n">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="K3" t="n">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="L3" t="n">
-        <v>0.2626653197836176</v>
+        <v>0.2610341569545225</v>
       </c>
       <c r="M3" t="n">
-        <v>4.445644162893681</v>
+        <v>4.446372119824862</v>
       </c>
       <c r="N3" t="n">
-        <v>33.71253946951741</v>
+        <v>33.69547910779995</v>
       </c>
       <c r="O3" t="n">
-        <v>5.806250035049938</v>
+        <v>5.804780711430877</v>
       </c>
       <c r="P3" t="n">
-        <v>341.2461875329175</v>
+        <v>341.2765021098598</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -32191,28 +32276,28 @@
         <v>0.07199999999999999</v>
       </c>
       <c r="I4" t="n">
-        <v>0.7538771549100625</v>
+        <v>0.7493583326069515</v>
       </c>
       <c r="J4" t="n">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="K4" t="n">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="L4" t="n">
-        <v>0.4460956820550462</v>
+        <v>0.4432165313844956</v>
       </c>
       <c r="M4" t="n">
-        <v>4.749288109691391</v>
+        <v>4.758106995246902</v>
       </c>
       <c r="N4" t="n">
-        <v>37.27915286393405</v>
+        <v>37.37169474230823</v>
       </c>
       <c r="O4" t="n">
-        <v>6.105665636434249</v>
+        <v>6.113239300265304</v>
       </c>
       <c r="P4" t="n">
-        <v>334.8311023958898</v>
+        <v>334.8799850037632</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -32269,28 +32354,28 @@
         <v>0.0653</v>
       </c>
       <c r="I5" t="n">
-        <v>0.7614137070780025</v>
+        <v>0.7592027222635589</v>
       </c>
       <c r="J5" t="n">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="K5" t="n">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="L5" t="n">
-        <v>0.4990467298662643</v>
+        <v>0.4986059278937913</v>
       </c>
       <c r="M5" t="n">
-        <v>4.232364792836694</v>
+        <v>4.230824827561118</v>
       </c>
       <c r="N5" t="n">
-        <v>30.74365665763525</v>
+        <v>30.70652001083286</v>
       </c>
       <c r="O5" t="n">
-        <v>5.544696263785353</v>
+        <v>5.541346407763447</v>
       </c>
       <c r="P5" t="n">
-        <v>341.5584411398566</v>
+        <v>341.582358589238</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -32347,28 +32432,28 @@
         <v>0.07149999999999999</v>
       </c>
       <c r="I6" t="n">
-        <v>0.7929407202920548</v>
+        <v>0.7929454214418066</v>
       </c>
       <c r="J6" t="n">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="K6" t="n">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="L6" t="n">
-        <v>0.4612155924712185</v>
+        <v>0.4626017684574822</v>
       </c>
       <c r="M6" t="n">
-        <v>4.615718953873372</v>
+        <v>4.6032022200811</v>
       </c>
       <c r="N6" t="n">
-        <v>38.801687832997</v>
+        <v>38.69624867368771</v>
       </c>
       <c r="O6" t="n">
-        <v>6.22910008211435</v>
+        <v>6.220630890326778</v>
       </c>
       <c r="P6" t="n">
-        <v>346.4886567293344</v>
+        <v>346.4886058743893</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -32425,28 +32510,28 @@
         <v>0.0478</v>
       </c>
       <c r="I7" t="n">
-        <v>0.6487689809361255</v>
+        <v>0.6476817764679804</v>
       </c>
       <c r="J7" t="n">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="K7" t="n">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="L7" t="n">
-        <v>0.4867895231276197</v>
+        <v>0.4872219724097232</v>
       </c>
       <c r="M7" t="n">
-        <v>3.693846382341294</v>
+        <v>3.688006971628252</v>
       </c>
       <c r="N7" t="n">
-        <v>23.44188781476359</v>
+        <v>23.38940784044889</v>
       </c>
       <c r="O7" t="n">
-        <v>4.841682333111455</v>
+        <v>4.836259695306786</v>
       </c>
       <c r="P7" t="n">
-        <v>356.7724505487553</v>
+        <v>356.784211442663</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -32503,28 +32588,28 @@
         <v>0.07240000000000001</v>
       </c>
       <c r="I8" t="n">
-        <v>0.6498661358999567</v>
+        <v>0.6479895281659366</v>
       </c>
       <c r="J8" t="n">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="K8" t="n">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="L8" t="n">
-        <v>0.4353359786442762</v>
+        <v>0.4349977062493794</v>
       </c>
       <c r="M8" t="n">
-        <v>4.138673806210758</v>
+        <v>4.135475650992077</v>
       </c>
       <c r="N8" t="n">
-        <v>28.93819953967361</v>
+        <v>28.89299407415566</v>
       </c>
       <c r="O8" t="n">
-        <v>5.379423718175917</v>
+        <v>5.375220374473558</v>
       </c>
       <c r="P8" t="n">
-        <v>354.8471624421367</v>
+        <v>354.8674627491284</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -32581,28 +32666,28 @@
         <v>0.0708</v>
       </c>
       <c r="I9" t="n">
-        <v>0.764665988090795</v>
+        <v>0.7633164647370493</v>
       </c>
       <c r="J9" t="n">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="K9" t="n">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="L9" t="n">
-        <v>0.5487823754351642</v>
+        <v>0.5491166522914974</v>
       </c>
       <c r="M9" t="n">
-        <v>3.912292186750653</v>
+        <v>3.908227520595227</v>
       </c>
       <c r="N9" t="n">
-        <v>25.39730207240339</v>
+        <v>25.34557637003661</v>
       </c>
       <c r="O9" t="n">
-        <v>5.039573600256612</v>
+        <v>5.034439032309023</v>
       </c>
       <c r="P9" t="n">
-        <v>347.7020754383014</v>
+        <v>347.7166739811278</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -32659,28 +32744,28 @@
         <v>0.0804</v>
       </c>
       <c r="I10" t="n">
-        <v>0.6225402387680365</v>
+        <v>0.6227293983114528</v>
       </c>
       <c r="J10" t="n">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="K10" t="n">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="L10" t="n">
-        <v>0.4583650093853396</v>
+        <v>0.4598944095418145</v>
       </c>
       <c r="M10" t="n">
-        <v>3.794288270362871</v>
+        <v>3.784861786403903</v>
       </c>
       <c r="N10" t="n">
-        <v>24.19291777793472</v>
+        <v>24.12751582431154</v>
       </c>
       <c r="O10" t="n">
-        <v>4.918629664645908</v>
+        <v>4.911976773592435</v>
       </c>
       <c r="P10" t="n">
-        <v>348.6178910917901</v>
+        <v>348.6158448480642</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -32737,28 +32822,28 @@
         <v>0.0702</v>
       </c>
       <c r="I11" t="n">
-        <v>0.5012399521345561</v>
+        <v>0.501700256529236</v>
       </c>
       <c r="J11" t="n">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="K11" t="n">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="L11" t="n">
-        <v>0.3738678500982183</v>
+        <v>0.3755806978771017</v>
       </c>
       <c r="M11" t="n">
-        <v>3.590802791305132</v>
+        <v>3.58340394586561</v>
       </c>
       <c r="N11" t="n">
-        <v>22.22784609059131</v>
+        <v>22.16945570463352</v>
       </c>
       <c r="O11" t="n">
-        <v>4.714641671494379</v>
+        <v>4.708445147246968</v>
       </c>
       <c r="P11" t="n">
-        <v>352.3168361248455</v>
+        <v>352.3118567568335</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -32815,28 +32900,28 @@
         <v>0.0683</v>
       </c>
       <c r="I12" t="n">
-        <v>0.7684426303269559</v>
+        <v>0.7662893704458432</v>
       </c>
       <c r="J12" t="n">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="K12" t="n">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="L12" t="n">
-        <v>0.5729670162588284</v>
+        <v>0.5724914570143902</v>
       </c>
       <c r="M12" t="n">
-        <v>3.78897746613096</v>
+        <v>3.788832841206963</v>
       </c>
       <c r="N12" t="n">
-        <v>23.24945820805475</v>
+        <v>23.23029470995286</v>
       </c>
       <c r="O12" t="n">
-        <v>4.821769198961595</v>
+        <v>4.819781603968468</v>
       </c>
       <c r="P12" t="n">
-        <v>346.503203737421</v>
+        <v>346.5264967441731</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -32893,28 +32978,28 @@
         <v>0.0834</v>
       </c>
       <c r="I13" t="n">
-        <v>0.7969733909883858</v>
+        <v>0.7957768819549995</v>
       </c>
       <c r="J13" t="n">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="K13" t="n">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="L13" t="n">
-        <v>0.5573285113001956</v>
+        <v>0.5578340016820391</v>
       </c>
       <c r="M13" t="n">
-        <v>4.086650696875969</v>
+        <v>4.081888850127733</v>
       </c>
       <c r="N13" t="n">
-        <v>26.65115722600033</v>
+        <v>26.59232604660773</v>
       </c>
       <c r="O13" t="n">
-        <v>5.162475881396476</v>
+        <v>5.156774771754893</v>
       </c>
       <c r="P13" t="n">
-        <v>340.2240391617577</v>
+        <v>340.2369824637893</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -32971,28 +33056,28 @@
         <v>0.163</v>
       </c>
       <c r="I14" t="n">
-        <v>0.8870029201924333</v>
+        <v>0.8858741242630488</v>
       </c>
       <c r="J14" t="n">
+        <v>368</v>
+      </c>
+      <c r="K14" t="n">
         <v>367</v>
       </c>
-      <c r="K14" t="n">
-        <v>366</v>
-      </c>
       <c r="L14" t="n">
-        <v>0.606782727057666</v>
+        <v>0.6073958642771802</v>
       </c>
       <c r="M14" t="n">
-        <v>3.920847805615085</v>
+        <v>3.915682300860941</v>
       </c>
       <c r="N14" t="n">
-        <v>26.84476029274307</v>
+        <v>26.78366469096286</v>
       </c>
       <c r="O14" t="n">
-        <v>5.181192941084425</v>
+        <v>5.175293681614876</v>
       </c>
       <c r="P14" t="n">
-        <v>334.6566829486219</v>
+        <v>334.6689299324505</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -33049,28 +33134,28 @@
         <v>0.1423</v>
       </c>
       <c r="I15" t="n">
-        <v>0.7552371160354451</v>
+        <v>0.7567931320321343</v>
       </c>
       <c r="J15" t="n">
+        <v>368</v>
+      </c>
+      <c r="K15" t="n">
         <v>367</v>
       </c>
-      <c r="K15" t="n">
-        <v>366</v>
-      </c>
       <c r="L15" t="n">
-        <v>0.5319645400302011</v>
+        <v>0.5341657060709509</v>
       </c>
       <c r="M15" t="n">
-        <v>4.026363119107017</v>
+        <v>4.023111476611742</v>
       </c>
       <c r="N15" t="n">
-        <v>26.23599505456263</v>
+        <v>26.18714530271663</v>
       </c>
       <c r="O15" t="n">
-        <v>5.12210845790702</v>
+        <v>5.117337716304898</v>
       </c>
       <c r="P15" t="n">
-        <v>333.7444390793809</v>
+        <v>333.727490158477</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -33127,28 +33212,28 @@
         <v>0.0774</v>
       </c>
       <c r="I16" t="n">
-        <v>0.6821195336562874</v>
+        <v>0.6824544763222352</v>
       </c>
       <c r="J16" t="n">
+        <v>368</v>
+      </c>
+      <c r="K16" t="n">
         <v>367</v>
       </c>
-      <c r="K16" t="n">
-        <v>366</v>
-      </c>
       <c r="L16" t="n">
-        <v>0.4958020279446168</v>
+        <v>0.4974347359854268</v>
       </c>
       <c r="M16" t="n">
-        <v>3.907072910063283</v>
+        <v>3.898022387086055</v>
       </c>
       <c r="N16" t="n">
-        <v>24.73708860283771</v>
+        <v>24.67073403098935</v>
       </c>
       <c r="O16" t="n">
-        <v>4.973639372012983</v>
+        <v>4.966964267134339</v>
       </c>
       <c r="P16" t="n">
-        <v>334.1766226424944</v>
+        <v>334.1729742759194</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -33205,28 +33290,28 @@
         <v>0.1178</v>
       </c>
       <c r="I17" t="n">
-        <v>0.8324560075089278</v>
+        <v>0.8308652252623283</v>
       </c>
       <c r="J17" t="n">
+        <v>368</v>
+      </c>
+      <c r="K17" t="n">
         <v>367</v>
       </c>
-      <c r="K17" t="n">
-        <v>366</v>
-      </c>
       <c r="L17" t="n">
-        <v>0.6167725446994285</v>
+        <v>0.6169410258588711</v>
       </c>
       <c r="M17" t="n">
-        <v>3.903943368454083</v>
+        <v>3.902018052328848</v>
       </c>
       <c r="N17" t="n">
-        <v>22.51069904677259</v>
+        <v>22.47302287229626</v>
       </c>
       <c r="O17" t="n">
-        <v>4.744544134769176</v>
+        <v>4.740571998429753</v>
       </c>
       <c r="P17" t="n">
-        <v>332.2700895295242</v>
+        <v>332.2874171421776</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -33283,28 +33368,28 @@
         <v>0.1043</v>
       </c>
       <c r="I18" t="n">
-        <v>0.8548985799711319</v>
+        <v>0.8564867837781942</v>
       </c>
       <c r="J18" t="n">
+        <v>368</v>
+      </c>
+      <c r="K18" t="n">
         <v>367</v>
       </c>
-      <c r="K18" t="n">
-        <v>366</v>
-      </c>
       <c r="L18" t="n">
-        <v>0.6227925767638438</v>
+        <v>0.6247363417006782</v>
       </c>
       <c r="M18" t="n">
-        <v>3.933477027350789</v>
+        <v>3.930652451123845</v>
       </c>
       <c r="N18" t="n">
-        <v>23.14199581347686</v>
+        <v>23.10252284441062</v>
       </c>
       <c r="O18" t="n">
-        <v>4.810612831384049</v>
+        <v>4.806508383890599</v>
       </c>
       <c r="P18" t="n">
-        <v>325.5540547614773</v>
+        <v>325.5367552345043</v>
       </c>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr">
@@ -33361,28 +33446,28 @@
         <v>0.1026</v>
       </c>
       <c r="I19" t="n">
-        <v>1.009363763660525</v>
+        <v>1.009322826719653</v>
       </c>
       <c r="J19" t="n">
+        <v>368</v>
+      </c>
+      <c r="K19" t="n">
         <v>367</v>
       </c>
-      <c r="K19" t="n">
-        <v>366</v>
-      </c>
       <c r="L19" t="n">
-        <v>0.7356867150426936</v>
+        <v>0.7367567315991104</v>
       </c>
       <c r="M19" t="n">
-        <v>3.579010424428741</v>
+        <v>3.56946871171506</v>
       </c>
       <c r="N19" t="n">
-        <v>19.13622696845335</v>
+        <v>19.08410032959826</v>
       </c>
       <c r="O19" t="n">
-        <v>4.374497338946882</v>
+        <v>4.368535261343127</v>
       </c>
       <c r="P19" t="n">
-        <v>319.4901170981457</v>
+        <v>319.4905630042124</v>
       </c>
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr">
@@ -33439,28 +33524,28 @@
         <v>0.1406</v>
       </c>
       <c r="I20" t="n">
-        <v>0.9775314231333863</v>
+        <v>0.9774094555120834</v>
       </c>
       <c r="J20" t="n">
+        <v>368</v>
+      </c>
+      <c r="K20" t="n">
         <v>367</v>
       </c>
-      <c r="K20" t="n">
-        <v>366</v>
-      </c>
       <c r="L20" t="n">
-        <v>0.6523570099092215</v>
+        <v>0.653566395676941</v>
       </c>
       <c r="M20" t="n">
-        <v>4.191470460320423</v>
+        <v>4.180580745369773</v>
       </c>
       <c r="N20" t="n">
-        <v>26.62222887591719</v>
+        <v>26.54982783358113</v>
       </c>
       <c r="O20" t="n">
-        <v>5.159673330349237</v>
+        <v>5.152652504640802</v>
       </c>
       <c r="P20" t="n">
-        <v>322.9748701004222</v>
+        <v>322.9761986340432</v>
       </c>
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr">
@@ -33517,28 +33602,28 @@
         <v>0.1091</v>
       </c>
       <c r="I21" t="n">
-        <v>0.8960784062844869</v>
+        <v>0.89611454596774</v>
       </c>
       <c r="J21" t="n">
+        <v>368</v>
+      </c>
+      <c r="K21" t="n">
         <v>367</v>
       </c>
-      <c r="K21" t="n">
-        <v>366</v>
-      </c>
       <c r="L21" t="n">
-        <v>0.5870968263927512</v>
+        <v>0.5884711355200696</v>
       </c>
       <c r="M21" t="n">
-        <v>4.377953738215081</v>
+        <v>4.366193683262797</v>
       </c>
       <c r="N21" t="n">
-        <v>29.52332909993087</v>
+        <v>29.44289627326716</v>
       </c>
       <c r="O21" t="n">
-        <v>5.433537438900267</v>
+        <v>5.426130875058872</v>
       </c>
       <c r="P21" t="n">
-        <v>332.9700794524986</v>
+        <v>332.9696858006118</v>
       </c>
       <c r="Q21" t="inlineStr"/>
       <c r="R21" t="inlineStr">
@@ -33595,28 +33680,28 @@
         <v>0.1106</v>
       </c>
       <c r="I22" t="n">
-        <v>0.8230734891307443</v>
+        <v>0.8223622621773978</v>
       </c>
       <c r="J22" t="n">
+        <v>368</v>
+      </c>
+      <c r="K22" t="n">
         <v>367</v>
       </c>
-      <c r="K22" t="n">
-        <v>366</v>
-      </c>
       <c r="L22" t="n">
-        <v>0.4840795003019319</v>
+        <v>0.4850129147394753</v>
       </c>
       <c r="M22" t="n">
-        <v>5.065437597234536</v>
+        <v>5.055608074615344</v>
       </c>
       <c r="N22" t="n">
-        <v>37.74662580038134</v>
+        <v>37.64850357448899</v>
       </c>
       <c r="O22" t="n">
-        <v>6.143828269115384</v>
+        <v>6.135837642448584</v>
       </c>
       <c r="P22" t="n">
-        <v>332.0106964393869</v>
+        <v>332.0184434865913</v>
       </c>
       <c r="Q22" t="inlineStr"/>
       <c r="R22" t="inlineStr">
@@ -33654,7 +33739,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W368"/>
+  <dimension ref="A1:W369"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -76673,6 +76758,123 @@
         </is>
       </c>
     </row>
+    <row r="369">
+      <c r="A369" s="1" t="inlineStr">
+        <is>
+          <t>2025-11-27 22:26:51+00:00</t>
+        </is>
+      </c>
+      <c r="B369" t="inlineStr">
+        <is>
+          <t>-44.15772413227122,168.24384993372362</t>
+        </is>
+      </c>
+      <c r="C369" t="inlineStr">
+        <is>
+          <t>-44.157707218015226,168.24483395368895</t>
+        </is>
+      </c>
+      <c r="D369" t="inlineStr">
+        <is>
+          <t>-44.15742471686104,168.2456405869523</t>
+        </is>
+      </c>
+      <c r="E369" t="inlineStr">
+        <is>
+          <t>-44.157033960640725,168.24636634968923</t>
+        </is>
+      </c>
+      <c r="F369" t="inlineStr">
+        <is>
+          <t>-44.15661843283369,168.24702672948027</t>
+        </is>
+      </c>
+      <c r="G369" t="inlineStr">
+        <is>
+          <t>-44.156173116063435,168.24765318176486</t>
+        </is>
+      </c>
+      <c r="H369" t="inlineStr">
+        <is>
+          <t>-44.15577441608249,168.2483580684502</t>
+        </is>
+      </c>
+      <c r="I369" t="inlineStr">
+        <is>
+          <t>-44.155374030494606,168.24906108028034</t>
+        </is>
+      </c>
+      <c r="J369" t="inlineStr">
+        <is>
+          <t>-44.15495114000288,168.2497390150971</t>
+        </is>
+      </c>
+      <c r="K369" t="inlineStr">
+        <is>
+          <t>-44.15452698493321,168.25039936735632</t>
+        </is>
+      </c>
+      <c r="L369" t="inlineStr">
+        <is>
+          <t>-44.154104513477044,168.25102755197855</t>
+        </is>
+      </c>
+      <c r="M369" t="inlineStr">
+        <is>
+          <t>-44.15360892099469,168.25157256553246</t>
+        </is>
+      </c>
+      <c r="N369" t="inlineStr">
+        <is>
+          <t>-44.15310036741865,168.25212325227818</t>
+        </is>
+      </c>
+      <c r="O369" t="inlineStr">
+        <is>
+          <t>-44.15257156946813,168.25263745013038</t>
+        </is>
+      </c>
+      <c r="P369" t="inlineStr">
+        <is>
+          <t>-44.152066900560136,168.253195157295</t>
+        </is>
+      </c>
+      <c r="Q369" t="inlineStr">
+        <is>
+          <t>-44.151554241229846,168.25372454721315</t>
+        </is>
+      </c>
+      <c r="R369" t="inlineStr">
+        <is>
+          <t>-44.15098018286312,168.25410116966145</t>
+        </is>
+      </c>
+      <c r="S369" t="inlineStr">
+        <is>
+          <t>-44.150405605716635,168.25450295621843</t>
+        </is>
+      </c>
+      <c r="T369" t="inlineStr">
+        <is>
+          <t>-44.14980139534716,168.25482085129977</t>
+        </is>
+      </c>
+      <c r="U369" t="inlineStr">
+        <is>
+          <t>-44.14918403607658,168.25506817870462</t>
+        </is>
+      </c>
+      <c r="V369" t="inlineStr">
+        <is>
+          <t>-44.14858120033506,168.25531969810348</t>
+        </is>
+      </c>
+      <c r="W369" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0455/nzd0455.xlsx
+++ b/data/nzd0455/nzd0455.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W369"/>
+  <dimension ref="A1:W370"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -28060,7 +28060,7 @@
         </is>
       </c>
       <c r="B369" t="n">
-        <v>383.67</v>
+        <v>379.36</v>
       </c>
       <c r="C369" t="n">
         <v>348.53</v>
@@ -28123,6 +28123,81 @@
         <v>352.34</v>
       </c>
       <c r="W369" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="370">
+      <c r="A370" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-29 22:26:48+00:00</t>
+        </is>
+      </c>
+      <c r="B370" t="n">
+        <v>380.16</v>
+      </c>
+      <c r="C370" t="n">
+        <v>346.85</v>
+      </c>
+      <c r="D370" t="n">
+        <v>345.85</v>
+      </c>
+      <c r="E370" t="n">
+        <v>357.26</v>
+      </c>
+      <c r="F370" t="n">
+        <v>369.35</v>
+      </c>
+      <c r="G370" t="n">
+        <v>371.37</v>
+      </c>
+      <c r="H370" t="n">
+        <v>369.39</v>
+      </c>
+      <c r="I370" t="n">
+        <v>366.96</v>
+      </c>
+      <c r="J370" t="n">
+        <v>368.48</v>
+      </c>
+      <c r="K370" t="n">
+        <v>368.47</v>
+      </c>
+      <c r="L370" t="n">
+        <v>364.86</v>
+      </c>
+      <c r="M370" t="n">
+        <v>357.76</v>
+      </c>
+      <c r="N370" t="n">
+        <v>353.73</v>
+      </c>
+      <c r="O370" t="n">
+        <v>356.11</v>
+      </c>
+      <c r="P370" t="n">
+        <v>352.44</v>
+      </c>
+      <c r="Q370" t="n">
+        <v>349.89</v>
+      </c>
+      <c r="R370" t="n">
+        <v>349.13</v>
+      </c>
+      <c r="S370" t="n">
+        <v>344.18</v>
+      </c>
+      <c r="T370" t="n">
+        <v>347.25</v>
+      </c>
+      <c r="U370" t="n">
+        <v>353.89</v>
+      </c>
+      <c r="V370" t="n">
+        <v>350.35</v>
+      </c>
+      <c r="W370" t="inlineStr">
         <is>
           <t>L8</t>
         </is>
@@ -28139,7 +28214,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B381"/>
+  <dimension ref="A1:B382"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -31952,6 +32027,16 @@
       </c>
       <c r="B381" t="n">
         <v>-0.6</v>
+      </c>
+    </row>
+    <row r="382">
+      <c r="A382" t="inlineStr">
+        <is>
+          <t>2025-12-29 22:30:00+00:00</t>
+        </is>
+      </c>
+      <c r="B382" t="n">
+        <v>-0.24</v>
       </c>
     </row>
   </sheetData>
@@ -32120,28 +32205,28 @@
         <v>0.0326</v>
       </c>
       <c r="I2" t="n">
-        <v>0.2563128187452734</v>
+        <v>0.2519362195241623</v>
       </c>
       <c r="J2" t="n">
+        <v>369</v>
+      </c>
+      <c r="K2" t="n">
         <v>368</v>
       </c>
-      <c r="K2" t="n">
-        <v>367</v>
-      </c>
       <c r="L2" t="n">
-        <v>0.02799525004571901</v>
+        <v>0.02719898856738268</v>
       </c>
       <c r="M2" t="n">
-        <v>7.881212268032868</v>
+        <v>7.885318545799281</v>
       </c>
       <c r="N2" t="n">
-        <v>120.4391319096421</v>
+        <v>120.211382981164</v>
       </c>
       <c r="O2" t="n">
-        <v>10.97447638430381</v>
+        <v>10.96409517384649</v>
       </c>
       <c r="P2" t="n">
-        <v>377.3106328771697</v>
+        <v>377.3582059328579</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -32198,28 +32283,28 @@
         <v>0.08740000000000001</v>
       </c>
       <c r="I3" t="n">
-        <v>0.4739970520647219</v>
+        <v>0.4703015427693388</v>
       </c>
       <c r="J3" t="n">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="K3" t="n">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="L3" t="n">
-        <v>0.2610341569545225</v>
+        <v>0.2583626123142563</v>
       </c>
       <c r="M3" t="n">
-        <v>4.446372119824862</v>
+        <v>4.451393178535445</v>
       </c>
       <c r="N3" t="n">
-        <v>33.69547910779995</v>
+        <v>33.73342959574298</v>
       </c>
       <c r="O3" t="n">
-        <v>5.804780711430877</v>
+        <v>5.808048690889478</v>
       </c>
       <c r="P3" t="n">
-        <v>341.2765021098598</v>
+        <v>341.316636116641</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -32276,28 +32361,28 @@
         <v>0.07199999999999999</v>
       </c>
       <c r="I4" t="n">
-        <v>0.7493583326069515</v>
+        <v>0.7446635243704718</v>
       </c>
       <c r="J4" t="n">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="K4" t="n">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="L4" t="n">
-        <v>0.4432165313844956</v>
+        <v>0.4401207083800339</v>
       </c>
       <c r="M4" t="n">
-        <v>4.758106995246902</v>
+        <v>4.767561190765758</v>
       </c>
       <c r="N4" t="n">
-        <v>37.37169474230823</v>
+        <v>37.47904411748818</v>
       </c>
       <c r="O4" t="n">
-        <v>6.113239300265304</v>
+        <v>6.122013077206564</v>
       </c>
       <c r="P4" t="n">
-        <v>334.8799850037632</v>
+        <v>334.930971606837</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -32354,28 +32439,28 @@
         <v>0.0653</v>
       </c>
       <c r="I5" t="n">
-        <v>0.7592027222635589</v>
+        <v>0.7568817818985027</v>
       </c>
       <c r="J5" t="n">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="K5" t="n">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="L5" t="n">
-        <v>0.4986059278937913</v>
+        <v>0.498058526037275</v>
       </c>
       <c r="M5" t="n">
-        <v>4.230824827561118</v>
+        <v>4.229698169866138</v>
       </c>
       <c r="N5" t="n">
-        <v>30.70652001083286</v>
+        <v>30.67429206339765</v>
       </c>
       <c r="O5" t="n">
-        <v>5.541346407763447</v>
+        <v>5.538437691569496</v>
       </c>
       <c r="P5" t="n">
-        <v>341.582358589238</v>
+        <v>341.6075644888595</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -32432,28 +32517,28 @@
         <v>0.07149999999999999</v>
       </c>
       <c r="I6" t="n">
-        <v>0.7929454214418066</v>
+        <v>0.7939748295144463</v>
       </c>
       <c r="J6" t="n">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="K6" t="n">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="L6" t="n">
-        <v>0.4626017684574822</v>
+        <v>0.4645743361338682</v>
       </c>
       <c r="M6" t="n">
-        <v>4.6032022200811</v>
+        <v>4.596392615990768</v>
       </c>
       <c r="N6" t="n">
-        <v>38.69624867368771</v>
+        <v>38.60141103177279</v>
       </c>
       <c r="O6" t="n">
-        <v>6.220630890326778</v>
+        <v>6.213003382565697</v>
       </c>
       <c r="P6" t="n">
-        <v>346.4886058743893</v>
+        <v>346.477426286607</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -32510,28 +32595,28 @@
         <v>0.0478</v>
       </c>
       <c r="I7" t="n">
-        <v>0.6476817764679804</v>
+        <v>0.6463436254785203</v>
       </c>
       <c r="J7" t="n">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="K7" t="n">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="L7" t="n">
-        <v>0.4872219724097232</v>
+        <v>0.4874055389333823</v>
       </c>
       <c r="M7" t="n">
-        <v>3.688006971628252</v>
+        <v>3.683119822072653</v>
       </c>
       <c r="N7" t="n">
-        <v>23.38940784044889</v>
+        <v>23.34297100398533</v>
       </c>
       <c r="O7" t="n">
-        <v>4.836259695306786</v>
+        <v>4.831456406093853</v>
       </c>
       <c r="P7" t="n">
-        <v>356.784211442663</v>
+        <v>356.7987440433392</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -32588,28 +32673,28 @@
         <v>0.07240000000000001</v>
       </c>
       <c r="I8" t="n">
-        <v>0.6479895281659366</v>
+        <v>0.6466125836511999</v>
       </c>
       <c r="J8" t="n">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="K8" t="n">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="L8" t="n">
-        <v>0.4349977062493794</v>
+        <v>0.4351747847131529</v>
       </c>
       <c r="M8" t="n">
-        <v>4.135475650992077</v>
+        <v>4.13015302624912</v>
       </c>
       <c r="N8" t="n">
-        <v>28.89299407415566</v>
+        <v>28.83263933636519</v>
       </c>
       <c r="O8" t="n">
-        <v>5.375220374473558</v>
+        <v>5.369603275509764</v>
       </c>
       <c r="P8" t="n">
-        <v>354.8674627491284</v>
+        <v>354.8824166556334</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -32666,28 +32751,28 @@
         <v>0.0708</v>
       </c>
       <c r="I9" t="n">
-        <v>0.7633164647370493</v>
+        <v>0.7628338779815733</v>
       </c>
       <c r="J9" t="n">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="K9" t="n">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="L9" t="n">
-        <v>0.5491166522914974</v>
+        <v>0.5501675494642436</v>
       </c>
       <c r="M9" t="n">
-        <v>3.908227520595227</v>
+        <v>3.899959534452786</v>
       </c>
       <c r="N9" t="n">
-        <v>25.34557637003661</v>
+        <v>25.27909355399109</v>
       </c>
       <c r="O9" t="n">
-        <v>5.034439032309023</v>
+        <v>5.027831893966931</v>
       </c>
       <c r="P9" t="n">
-        <v>347.7166739811278</v>
+        <v>347.7219149746063</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -32744,28 +32829,28 @@
         <v>0.0804</v>
       </c>
       <c r="I10" t="n">
-        <v>0.6227293983114528</v>
+        <v>0.6245586130146286</v>
       </c>
       <c r="J10" t="n">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="K10" t="n">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="L10" t="n">
-        <v>0.4598944095418145</v>
+        <v>0.4624161777794029</v>
       </c>
       <c r="M10" t="n">
-        <v>3.784861786403903</v>
+        <v>3.783095272073778</v>
       </c>
       <c r="N10" t="n">
-        <v>24.12751582431154</v>
+        <v>24.09380088006874</v>
       </c>
       <c r="O10" t="n">
-        <v>4.911976773592435</v>
+        <v>4.908543661827685</v>
       </c>
       <c r="P10" t="n">
-        <v>348.6158448480642</v>
+        <v>348.5959791923633</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -32822,28 +32907,28 @@
         <v>0.0702</v>
       </c>
       <c r="I11" t="n">
-        <v>0.501700256529236</v>
+        <v>0.5032522366803206</v>
       </c>
       <c r="J11" t="n">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="K11" t="n">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="L11" t="n">
-        <v>0.3755806978771017</v>
+        <v>0.3781037700762956</v>
       </c>
       <c r="M11" t="n">
-        <v>3.58340394586561</v>
+        <v>3.581623638160499</v>
       </c>
       <c r="N11" t="n">
-        <v>22.16945570463352</v>
+        <v>22.13217449780726</v>
       </c>
       <c r="O11" t="n">
-        <v>4.708445147246968</v>
+        <v>4.704484509253618</v>
       </c>
       <c r="P11" t="n">
-        <v>352.3118567568335</v>
+        <v>352.2950019265708</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -32900,28 +32985,28 @@
         <v>0.0683</v>
       </c>
       <c r="I12" t="n">
-        <v>0.7662893704458432</v>
+        <v>0.765282448123384</v>
       </c>
       <c r="J12" t="n">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="K12" t="n">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="L12" t="n">
-        <v>0.5724914570143902</v>
+        <v>0.5731163126136702</v>
       </c>
       <c r="M12" t="n">
-        <v>3.788832841206963</v>
+        <v>3.78328275245918</v>
       </c>
       <c r="N12" t="n">
-        <v>23.23029470995286</v>
+        <v>23.17693681948478</v>
       </c>
       <c r="O12" t="n">
-        <v>4.819781603968468</v>
+        <v>4.814243120105671</v>
       </c>
       <c r="P12" t="n">
-        <v>346.5264967441731</v>
+        <v>346.5374321319877</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -32978,28 +33063,28 @@
         <v>0.0834</v>
       </c>
       <c r="I13" t="n">
-        <v>0.7957768819549995</v>
+        <v>0.7939212853640598</v>
       </c>
       <c r="J13" t="n">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="K13" t="n">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="L13" t="n">
-        <v>0.5578340016820391</v>
+        <v>0.5577600691927389</v>
       </c>
       <c r="M13" t="n">
-        <v>4.081888850127733</v>
+        <v>4.08055849944023</v>
       </c>
       <c r="N13" t="n">
-        <v>26.59232604660773</v>
+        <v>26.55285154711987</v>
       </c>
       <c r="O13" t="n">
-        <v>5.156774771754893</v>
+        <v>5.152945909586076</v>
       </c>
       <c r="P13" t="n">
-        <v>340.2369824637893</v>
+        <v>340.2571346323298</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -33056,28 +33141,28 @@
         <v>0.163</v>
       </c>
       <c r="I14" t="n">
-        <v>0.8858741242630488</v>
+        <v>0.883564882452739</v>
       </c>
       <c r="J14" t="n">
+        <v>369</v>
+      </c>
+      <c r="K14" t="n">
         <v>368</v>
       </c>
-      <c r="K14" t="n">
-        <v>367</v>
-      </c>
       <c r="L14" t="n">
-        <v>0.6073958642771802</v>
+        <v>0.6070377857601155</v>
       </c>
       <c r="M14" t="n">
-        <v>3.915682300860941</v>
+        <v>3.916346443979021</v>
       </c>
       <c r="N14" t="n">
-        <v>26.78366469096286</v>
+        <v>26.76116884556399</v>
       </c>
       <c r="O14" t="n">
-        <v>5.175293681614876</v>
+        <v>5.173119836768136</v>
       </c>
       <c r="P14" t="n">
-        <v>334.6689299324505</v>
+        <v>334.6940830123077</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -33134,28 +33219,28 @@
         <v>0.1423</v>
       </c>
       <c r="I15" t="n">
-        <v>0.7567931320321343</v>
+        <v>0.7580865401273504</v>
       </c>
       <c r="J15" t="n">
+        <v>369</v>
+      </c>
+      <c r="K15" t="n">
         <v>368</v>
       </c>
-      <c r="K15" t="n">
-        <v>367</v>
-      </c>
       <c r="L15" t="n">
-        <v>0.5341657060709509</v>
+        <v>0.5362658889691796</v>
       </c>
       <c r="M15" t="n">
-        <v>4.023111476611742</v>
+        <v>4.018519604592219</v>
       </c>
       <c r="N15" t="n">
-        <v>26.18714530271663</v>
+        <v>26.13158050672673</v>
       </c>
       <c r="O15" t="n">
-        <v>5.117337716304898</v>
+        <v>5.111905760743905</v>
       </c>
       <c r="P15" t="n">
-        <v>333.727490158477</v>
+        <v>333.7133466401414</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -33212,28 +33297,28 @@
         <v>0.0774</v>
       </c>
       <c r="I16" t="n">
-        <v>0.6824544763222352</v>
+        <v>0.6825922932993563</v>
       </c>
       <c r="J16" t="n">
+        <v>369</v>
+      </c>
+      <c r="K16" t="n">
         <v>368</v>
       </c>
-      <c r="K16" t="n">
-        <v>367</v>
-      </c>
       <c r="L16" t="n">
-        <v>0.4974347359854268</v>
+        <v>0.4989399809364947</v>
       </c>
       <c r="M16" t="n">
-        <v>3.898022387086055</v>
+        <v>3.888078788227847</v>
       </c>
       <c r="N16" t="n">
-        <v>24.67073403098935</v>
+        <v>24.60387106304076</v>
       </c>
       <c r="O16" t="n">
-        <v>4.966964267134339</v>
+        <v>4.960228932523252</v>
       </c>
       <c r="P16" t="n">
-        <v>334.1729742759194</v>
+        <v>334.1714672365325</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -33290,28 +33375,28 @@
         <v>0.1178</v>
       </c>
       <c r="I17" t="n">
-        <v>0.8308652252623283</v>
+        <v>0.8285385248387811</v>
       </c>
       <c r="J17" t="n">
+        <v>369</v>
+      </c>
+      <c r="K17" t="n">
         <v>368</v>
       </c>
-      <c r="K17" t="n">
-        <v>367</v>
-      </c>
       <c r="L17" t="n">
-        <v>0.6169410258588711</v>
+        <v>0.6164130714929761</v>
       </c>
       <c r="M17" t="n">
-        <v>3.902018052328848</v>
+        <v>3.904020869607985</v>
       </c>
       <c r="N17" t="n">
-        <v>22.47302287229626</v>
+        <v>22.46242343666826</v>
       </c>
       <c r="O17" t="n">
-        <v>4.740571998429753</v>
+        <v>4.739453917559307</v>
       </c>
       <c r="P17" t="n">
-        <v>332.2874171421776</v>
+        <v>332.3128597926631</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -33368,28 +33453,28 @@
         <v>0.1043</v>
       </c>
       <c r="I18" t="n">
-        <v>0.8564867837781942</v>
+        <v>0.8570180235940409</v>
       </c>
       <c r="J18" t="n">
+        <v>369</v>
+      </c>
+      <c r="K18" t="n">
         <v>368</v>
       </c>
-      <c r="K18" t="n">
-        <v>367</v>
-      </c>
       <c r="L18" t="n">
-        <v>0.6247363417006782</v>
+        <v>0.6263175624859914</v>
       </c>
       <c r="M18" t="n">
-        <v>3.930652451123845</v>
+        <v>3.922581057416161</v>
       </c>
       <c r="N18" t="n">
-        <v>23.10252284441062</v>
+        <v>23.0423752519885</v>
       </c>
       <c r="O18" t="n">
-        <v>4.806508383890599</v>
+        <v>4.800247415705622</v>
       </c>
       <c r="P18" t="n">
-        <v>325.5367552345043</v>
+        <v>325.5309460857107</v>
       </c>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr">
@@ -33446,28 +33531,28 @@
         <v>0.1026</v>
       </c>
       <c r="I19" t="n">
-        <v>1.009322826719653</v>
+        <v>1.00827238729423</v>
       </c>
       <c r="J19" t="n">
+        <v>369</v>
+      </c>
+      <c r="K19" t="n">
         <v>368</v>
       </c>
-      <c r="K19" t="n">
-        <v>367</v>
-      </c>
       <c r="L19" t="n">
-        <v>0.7367567315991104</v>
+        <v>0.7373384489835344</v>
       </c>
       <c r="M19" t="n">
-        <v>3.56946871171506</v>
+        <v>3.56510579171803</v>
       </c>
       <c r="N19" t="n">
-        <v>19.08410032959826</v>
+        <v>19.04252820199344</v>
       </c>
       <c r="O19" t="n">
-        <v>4.368535261343127</v>
+        <v>4.363774536109014</v>
       </c>
       <c r="P19" t="n">
-        <v>319.4905630042124</v>
+        <v>319.5020496412056</v>
       </c>
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr">
@@ -33524,28 +33609,28 @@
         <v>0.1406</v>
       </c>
       <c r="I20" t="n">
-        <v>0.9774094555120834</v>
+        <v>0.9765930098924861</v>
       </c>
       <c r="J20" t="n">
+        <v>369</v>
+      </c>
+      <c r="K20" t="n">
         <v>368</v>
       </c>
-      <c r="K20" t="n">
-        <v>367</v>
-      </c>
       <c r="L20" t="n">
-        <v>0.653566395676941</v>
+        <v>0.6544078272212521</v>
       </c>
       <c r="M20" t="n">
-        <v>4.180580745369773</v>
+        <v>4.172732919827648</v>
       </c>
       <c r="N20" t="n">
-        <v>26.54982783358113</v>
+        <v>26.48389589517747</v>
       </c>
       <c r="O20" t="n">
-        <v>5.152652504640802</v>
+        <v>5.146250663850088</v>
       </c>
       <c r="P20" t="n">
-        <v>322.9761986340432</v>
+        <v>322.9851265305311</v>
       </c>
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr">
@@ -33602,28 +33687,28 @@
         <v>0.1091</v>
       </c>
       <c r="I21" t="n">
-        <v>0.89611454596774</v>
+        <v>0.8946456198967926</v>
       </c>
       <c r="J21" t="n">
+        <v>369</v>
+      </c>
+      <c r="K21" t="n">
         <v>368</v>
       </c>
-      <c r="K21" t="n">
-        <v>367</v>
-      </c>
       <c r="L21" t="n">
-        <v>0.5884711355200696</v>
+        <v>0.5888727071397601</v>
       </c>
       <c r="M21" t="n">
-        <v>4.366193683262797</v>
+        <v>4.362261974664419</v>
       </c>
       <c r="N21" t="n">
-        <v>29.44289627326716</v>
+        <v>29.38300432132882</v>
       </c>
       <c r="O21" t="n">
-        <v>5.426130875058872</v>
+        <v>5.420609220496236</v>
       </c>
       <c r="P21" t="n">
-        <v>332.9696858006118</v>
+        <v>332.9857486216927</v>
       </c>
       <c r="Q21" t="inlineStr"/>
       <c r="R21" t="inlineStr">
@@ -33680,28 +33765,28 @@
         <v>0.1106</v>
       </c>
       <c r="I22" t="n">
-        <v>0.8223622621773978</v>
+        <v>0.8205480498133799</v>
       </c>
       <c r="J22" t="n">
+        <v>369</v>
+      </c>
+      <c r="K22" t="n">
         <v>368</v>
       </c>
-      <c r="K22" t="n">
-        <v>367</v>
-      </c>
       <c r="L22" t="n">
-        <v>0.4850129147394753</v>
+        <v>0.4851104365853913</v>
       </c>
       <c r="M22" t="n">
-        <v>5.055608074615344</v>
+        <v>5.051894006400448</v>
       </c>
       <c r="N22" t="n">
-        <v>37.64850357448899</v>
+        <v>37.5768821590568</v>
       </c>
       <c r="O22" t="n">
-        <v>6.135837642448584</v>
+        <v>6.129998544784232</v>
       </c>
       <c r="P22" t="n">
-        <v>332.0184434865913</v>
+        <v>332.0382820402002</v>
       </c>
       <c r="Q22" t="inlineStr"/>
       <c r="R22" t="inlineStr">
@@ -33739,7 +33824,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W369"/>
+  <dimension ref="A1:W370"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -76766,7 +76851,7 @@
       </c>
       <c r="B369" t="inlineStr">
         <is>
-          <t>-44.15772413227122,168.24384993372362</t>
+          <t>-44.157759041476766,168.24387324982422</t>
         </is>
       </c>
       <c r="C369" t="inlineStr">
@@ -76870,6 +76955,123 @@
         </is>
       </c>
       <c r="W369" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="370">
+      <c r="A370" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-29 22:26:48+00:00</t>
+        </is>
+      </c>
+      <c r="B370" t="inlineStr">
+        <is>
+          <t>-44.15775256181013,168.24386892200772</t>
+        </is>
+      </c>
+      <c r="C370" t="inlineStr">
+        <is>
+          <t>-44.15772082526832,168.2448430422677</t>
+        </is>
+      </c>
+      <c r="D370" t="inlineStr">
+        <is>
+          <t>-44.1574273897071,168.2456423722269</t>
+        </is>
+      </c>
+      <c r="E370" t="inlineStr">
+        <is>
+          <t>-44.15703538623624,168.24636741179523</t>
+        </is>
+      </c>
+      <c r="F370" t="inlineStr">
+        <is>
+          <t>-44.156603739262366,168.2470125667375</t>
+        </is>
+      </c>
+      <c r="G370" t="inlineStr">
+        <is>
+          <t>-44.156176130348285,168.24765654098437</t>
+        </is>
+      </c>
+      <c r="H370" t="inlineStr">
+        <is>
+          <t>-44.15576761644674,168.248350490665</t>
+        </is>
+      </c>
+      <c r="I370" t="inlineStr">
+        <is>
+          <t>-44.155362253858094,168.24904795584965</t>
+        </is>
+      </c>
+      <c r="J370" t="inlineStr">
+        <is>
+          <t>-44.15492919909958,168.24971456301742</t>
+        </is>
+      </c>
+      <c r="K370" t="inlineStr">
+        <is>
+          <t>-44.154512800122966,168.25038207500313</t>
+        </is>
+      </c>
+      <c r="L370" t="inlineStr">
+        <is>
+          <t>-44.15409143383903,168.25100729095664</t>
+        </is>
+      </c>
+      <c r="M370" t="inlineStr">
+        <is>
+          <t>-44.153615393323754,168.2515842340842</t>
+        </is>
+      </c>
+      <c r="N370" t="inlineStr">
+        <is>
+          <t>-44.15311216014775,168.25214451268656</t>
+        </is>
+      </c>
+      <c r="O370" t="inlineStr">
+        <is>
+          <t>-44.15257376345207,168.25264140553497</t>
+        </is>
+      </c>
+      <c r="P370" t="inlineStr">
+        <is>
+          <t>-44.15206854603776,168.2531981238362</t>
+        </is>
+      </c>
+      <c r="Q370" t="inlineStr">
+        <is>
+          <t>-44.15156062083542,168.25373843895568</t>
+        </is>
+      </c>
+      <c r="R370" t="inlineStr">
+        <is>
+          <t>-44.150987589917605,168.25412212257683</t>
+        </is>
+      </c>
+      <c r="S370" t="inlineStr">
+        <is>
+          <t>-44.15041237229748,168.2545232270492</t>
+        </is>
+      </c>
+      <c r="T370" t="inlineStr">
+        <is>
+          <t>-44.14980596937608,168.25483455381035</t>
+        </is>
+      </c>
+      <c r="U370" t="inlineStr">
+        <is>
+          <t>-44.14919249559213,168.25510003233032</t>
+        </is>
+      </c>
+      <c r="V370" t="inlineStr">
+        <is>
+          <t>-44.14858600387828,168.25534362457972</t>
+        </is>
+      </c>
+      <c r="W370" t="inlineStr">
         <is>
           <t>L8</t>
         </is>

--- a/data/nzd0455/nzd0455.xlsx
+++ b/data/nzd0455/nzd0455.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W370"/>
+  <dimension ref="A1:W373"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -28200,6 +28200,231 @@
       <c r="W370" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="371">
+      <c r="A371" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-07 22:26:48+00:00</t>
+        </is>
+      </c>
+      <c r="B371" t="n">
+        <v>379.46</v>
+      </c>
+      <c r="C371" t="n">
+        <v>347.97</v>
+      </c>
+      <c r="D371" t="n">
+        <v>345.36</v>
+      </c>
+      <c r="E371" t="n">
+        <v>356.52</v>
+      </c>
+      <c r="F371" t="n">
+        <v>366.99</v>
+      </c>
+      <c r="G371" t="n">
+        <v>368.92</v>
+      </c>
+      <c r="H371" t="n">
+        <v>369.46</v>
+      </c>
+      <c r="I371" t="n">
+        <v>365.53</v>
+      </c>
+      <c r="J371" t="n">
+        <v>368.56</v>
+      </c>
+      <c r="K371" t="n">
+        <v>367.49</v>
+      </c>
+      <c r="L371" t="n">
+        <v>363.9</v>
+      </c>
+      <c r="M371" t="n">
+        <v>358.35</v>
+      </c>
+      <c r="N371" t="n">
+        <v>353.42</v>
+      </c>
+      <c r="O371" t="n">
+        <v>354.99</v>
+      </c>
+      <c r="P371" t="n">
+        <v>352.02</v>
+      </c>
+      <c r="Q371" t="n">
+        <v>349.25</v>
+      </c>
+      <c r="R371" t="n">
+        <v>349.37</v>
+      </c>
+      <c r="S371" t="n">
+        <v>341.26</v>
+      </c>
+      <c r="T371" t="n">
+        <v>344.53</v>
+      </c>
+      <c r="U371" t="n">
+        <v>353.31</v>
+      </c>
+      <c r="V371" t="n">
+        <v>350.99</v>
+      </c>
+      <c r="W371" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="372">
+      <c r="A372" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-15 22:26:35+00:00</t>
+        </is>
+      </c>
+      <c r="B372" t="n">
+        <v>380.98</v>
+      </c>
+      <c r="C372" t="n">
+        <v>349.18</v>
+      </c>
+      <c r="D372" t="n">
+        <v>347.14</v>
+      </c>
+      <c r="E372" t="n">
+        <v>357.3</v>
+      </c>
+      <c r="F372" t="n">
+        <v>366.78</v>
+      </c>
+      <c r="G372" t="n">
+        <v>369.2</v>
+      </c>
+      <c r="H372" t="n">
+        <v>369.67</v>
+      </c>
+      <c r="I372" t="n">
+        <v>365.91</v>
+      </c>
+      <c r="J372" t="n">
+        <v>368.44</v>
+      </c>
+      <c r="K372" t="n">
+        <v>368.15</v>
+      </c>
+      <c r="L372" t="n">
+        <v>364.21</v>
+      </c>
+      <c r="M372" t="n">
+        <v>359.31</v>
+      </c>
+      <c r="N372" t="n">
+        <v>354.45</v>
+      </c>
+      <c r="O372" t="n">
+        <v>355.11</v>
+      </c>
+      <c r="P372" t="n">
+        <v>353.31</v>
+      </c>
+      <c r="Q372" t="n">
+        <v>349.81</v>
+      </c>
+      <c r="R372" t="n">
+        <v>348.99</v>
+      </c>
+      <c r="S372" t="n">
+        <v>340.88</v>
+      </c>
+      <c r="T372" t="n">
+        <v>344.08</v>
+      </c>
+      <c r="U372" t="n">
+        <v>353.85</v>
+      </c>
+      <c r="V372" t="n">
+        <v>351.7</v>
+      </c>
+      <c r="W372" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="373">
+      <c r="A373" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-23 22:26:42+00:00</t>
+        </is>
+      </c>
+      <c r="B373" t="n">
+        <v>385.47</v>
+      </c>
+      <c r="C373" t="n">
+        <v>350.3</v>
+      </c>
+      <c r="D373" t="n">
+        <v>347.5</v>
+      </c>
+      <c r="E373" t="n">
+        <v>357.28</v>
+      </c>
+      <c r="F373" t="n">
+        <v>365.55</v>
+      </c>
+      <c r="G373" t="n">
+        <v>369.55</v>
+      </c>
+      <c r="H373" t="n">
+        <v>369.26</v>
+      </c>
+      <c r="I373" t="n">
+        <v>366.25</v>
+      </c>
+      <c r="J373" t="n">
+        <v>368.62</v>
+      </c>
+      <c r="K373" t="n">
+        <v>368.23</v>
+      </c>
+      <c r="L373" t="n">
+        <v>364.74</v>
+      </c>
+      <c r="M373" t="n">
+        <v>358.68</v>
+      </c>
+      <c r="N373" t="n">
+        <v>355.69</v>
+      </c>
+      <c r="O373" t="n">
+        <v>356.23</v>
+      </c>
+      <c r="P373" t="n">
+        <v>354.44</v>
+      </c>
+      <c r="Q373" t="n">
+        <v>353.59</v>
+      </c>
+      <c r="R373" t="n">
+        <v>349.12</v>
+      </c>
+      <c r="S373" t="n">
+        <v>343.05</v>
+      </c>
+      <c r="T373" t="n">
+        <v>344.31</v>
+      </c>
+      <c r="U373" t="n">
+        <v>354.24</v>
+      </c>
+      <c r="V373" t="n">
+        <v>352.88</v>
+      </c>
+      <c r="W373" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
@@ -28214,7 +28439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B382"/>
+  <dimension ref="A1:B385"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -32037,6 +32262,36 @@
       </c>
       <c r="B382" t="n">
         <v>-0.24</v>
+      </c>
+    </row>
+    <row r="383">
+      <c r="A383" t="inlineStr">
+        <is>
+          <t>2026-02-07 22:30:00+00:00</t>
+        </is>
+      </c>
+      <c r="B383" t="n">
+        <v>-0.61</v>
+      </c>
+    </row>
+    <row r="384">
+      <c r="A384" t="inlineStr">
+        <is>
+          <t>2026-02-15 22:30:00+00:00</t>
+        </is>
+      </c>
+      <c r="B384" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+    </row>
+    <row r="385">
+      <c r="A385" t="inlineStr">
+        <is>
+          <t>2026-02-23 22:30:00+00:00</t>
+        </is>
+      </c>
+      <c r="B385" t="n">
+        <v>-0.76</v>
       </c>
     </row>
   </sheetData>
@@ -32205,28 +32460,28 @@
         <v>0.0326</v>
       </c>
       <c r="I2" t="n">
-        <v>0.2519362195241623</v>
+        <v>0.2486622145863311</v>
       </c>
       <c r="J2" t="n">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="K2" t="n">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="L2" t="n">
-        <v>0.02719898856738268</v>
+        <v>0.02693472608936698</v>
       </c>
       <c r="M2" t="n">
-        <v>7.885318545799281</v>
+        <v>7.84835582331841</v>
       </c>
       <c r="N2" t="n">
-        <v>120.211382981164</v>
+        <v>119.3256448633128</v>
       </c>
       <c r="O2" t="n">
-        <v>10.96409517384649</v>
+        <v>10.92362782519218</v>
       </c>
       <c r="P2" t="n">
-        <v>377.3582059328579</v>
+        <v>377.3940410283958</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -32283,28 +32538,28 @@
         <v>0.08740000000000001</v>
       </c>
       <c r="I3" t="n">
-        <v>0.4703015427693388</v>
+        <v>0.4629810356600254</v>
       </c>
       <c r="J3" t="n">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="K3" t="n">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="L3" t="n">
-        <v>0.2583626123142563</v>
+        <v>0.2545884342201895</v>
       </c>
       <c r="M3" t="n">
-        <v>4.451393178535445</v>
+        <v>4.449649267016144</v>
       </c>
       <c r="N3" t="n">
-        <v>33.73342959574298</v>
+        <v>33.63779773972621</v>
       </c>
       <c r="O3" t="n">
-        <v>5.808048690889478</v>
+        <v>5.799810146869138</v>
       </c>
       <c r="P3" t="n">
-        <v>341.316636116641</v>
+        <v>341.396587915179</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -32361,28 +32616,28 @@
         <v>0.07199999999999999</v>
       </c>
       <c r="I4" t="n">
-        <v>0.7446635243704718</v>
+        <v>0.7320081421659598</v>
       </c>
       <c r="J4" t="n">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="K4" t="n">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="L4" t="n">
-        <v>0.4401207083800339</v>
+        <v>0.4324649578139742</v>
       </c>
       <c r="M4" t="n">
-        <v>4.767561190765758</v>
+        <v>4.788440487961488</v>
       </c>
       <c r="N4" t="n">
-        <v>37.47904411748818</v>
+        <v>37.68923101936049</v>
       </c>
       <c r="O4" t="n">
-        <v>6.122013077206564</v>
+        <v>6.13915556240111</v>
       </c>
       <c r="P4" t="n">
-        <v>334.930971606837</v>
+        <v>335.0691995106314</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -32439,28 +32694,28 @@
         <v>0.0653</v>
       </c>
       <c r="I5" t="n">
-        <v>0.7568817818985027</v>
+        <v>0.7495379115994859</v>
       </c>
       <c r="J5" t="n">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="K5" t="n">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="L5" t="n">
-        <v>0.498058526037275</v>
+        <v>0.4959911535511148</v>
       </c>
       <c r="M5" t="n">
-        <v>4.229698169866138</v>
+        <v>4.228862920609981</v>
       </c>
       <c r="N5" t="n">
-        <v>30.67429206339765</v>
+        <v>30.5981473197931</v>
       </c>
       <c r="O5" t="n">
-        <v>5.538437691569496</v>
+        <v>5.531559212355328</v>
       </c>
       <c r="P5" t="n">
-        <v>341.6075644888595</v>
+        <v>341.6877803727527</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -32517,28 +32772,28 @@
         <v>0.07149999999999999</v>
       </c>
       <c r="I6" t="n">
-        <v>0.7939748295144463</v>
+        <v>0.7922414993885674</v>
       </c>
       <c r="J6" t="n">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="K6" t="n">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="L6" t="n">
-        <v>0.4645743361338682</v>
+        <v>0.4675942131305895</v>
       </c>
       <c r="M6" t="n">
-        <v>4.596392615990768</v>
+        <v>4.567294639713853</v>
       </c>
       <c r="N6" t="n">
-        <v>38.60141103177279</v>
+        <v>38.30297520167677</v>
       </c>
       <c r="O6" t="n">
-        <v>6.213003382565697</v>
+        <v>6.188939747782069</v>
       </c>
       <c r="P6" t="n">
-        <v>346.477426286607</v>
+        <v>346.4963684320909</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -32595,28 +32850,28 @@
         <v>0.0478</v>
       </c>
       <c r="I7" t="n">
-        <v>0.6463436254785203</v>
+        <v>0.6388959758891245</v>
       </c>
       <c r="J7" t="n">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="K7" t="n">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="L7" t="n">
-        <v>0.4874055389333823</v>
+        <v>0.4839359370222082</v>
       </c>
       <c r="M7" t="n">
-        <v>3.683119822072653</v>
+        <v>3.682059759560806</v>
       </c>
       <c r="N7" t="n">
-        <v>23.34297100398533</v>
+        <v>23.3302688001786</v>
       </c>
       <c r="O7" t="n">
-        <v>4.831456406093853</v>
+        <v>4.830141695662623</v>
       </c>
       <c r="P7" t="n">
-        <v>356.7987440433392</v>
+        <v>356.8800942817863</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -32673,28 +32928,28 @@
         <v>0.07240000000000001</v>
       </c>
       <c r="I8" t="n">
-        <v>0.6466125836511999</v>
+        <v>0.6425580921972022</v>
       </c>
       <c r="J8" t="n">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="K8" t="n">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="L8" t="n">
-        <v>0.4351747847131529</v>
+        <v>0.4357750412572063</v>
       </c>
       <c r="M8" t="n">
-        <v>4.13015302624912</v>
+        <v>4.113967627212819</v>
       </c>
       <c r="N8" t="n">
-        <v>28.83263933636519</v>
+        <v>28.65223003666696</v>
       </c>
       <c r="O8" t="n">
-        <v>5.369603275509764</v>
+        <v>5.352777786968833</v>
       </c>
       <c r="P8" t="n">
-        <v>354.8824166556334</v>
+        <v>354.9267067643892</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -32751,28 +33006,28 @@
         <v>0.0708</v>
       </c>
       <c r="I9" t="n">
-        <v>0.7628338779815733</v>
+        <v>0.7595851151147518</v>
       </c>
       <c r="J9" t="n">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="K9" t="n">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="L9" t="n">
-        <v>0.5501675494642436</v>
+        <v>0.5518878473282277</v>
       </c>
       <c r="M9" t="n">
-        <v>3.899959534452786</v>
+        <v>3.884204707666886</v>
       </c>
       <c r="N9" t="n">
-        <v>25.27909355399109</v>
+        <v>25.10917689139512</v>
       </c>
       <c r="O9" t="n">
-        <v>5.027831893966931</v>
+        <v>5.010905795501959</v>
       </c>
       <c r="P9" t="n">
-        <v>347.7219149746063</v>
+        <v>347.7573986580551</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -32829,28 +33084,28 @@
         <v>0.0804</v>
       </c>
       <c r="I10" t="n">
-        <v>0.6245586130146286</v>
+        <v>0.6298959937002301</v>
       </c>
       <c r="J10" t="n">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="K10" t="n">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="L10" t="n">
-        <v>0.4624161777794029</v>
+        <v>0.4699079153433245</v>
       </c>
       <c r="M10" t="n">
-        <v>3.783095272073778</v>
+        <v>3.777570373029868</v>
       </c>
       <c r="N10" t="n">
-        <v>24.09380088006874</v>
+        <v>23.98943087651378</v>
       </c>
       <c r="O10" t="n">
-        <v>4.908543661827685</v>
+        <v>4.897900660131214</v>
       </c>
       <c r="P10" t="n">
-        <v>348.5959791923633</v>
+        <v>348.5376766703165</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -32907,28 +33162,28 @@
         <v>0.0702</v>
       </c>
       <c r="I11" t="n">
-        <v>0.5032522366803206</v>
+        <v>0.5069051360762543</v>
       </c>
       <c r="J11" t="n">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="K11" t="n">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="L11" t="n">
-        <v>0.3781037700762956</v>
+        <v>0.3850304503379364</v>
       </c>
       <c r="M11" t="n">
-        <v>3.581623638160499</v>
+        <v>3.571009177006828</v>
       </c>
       <c r="N11" t="n">
-        <v>22.13217449780726</v>
+        <v>21.99660276003265</v>
       </c>
       <c r="O11" t="n">
-        <v>4.704484509253618</v>
+        <v>4.69005359884433</v>
       </c>
       <c r="P11" t="n">
-        <v>352.2950019265708</v>
+        <v>352.2550958950198</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -32985,28 +33240,28 @@
         <v>0.0683</v>
       </c>
       <c r="I12" t="n">
-        <v>0.765282448123384</v>
+        <v>0.7612515732009105</v>
       </c>
       <c r="J12" t="n">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="K12" t="n">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="L12" t="n">
-        <v>0.5731163126136702</v>
+        <v>0.5740977082779773</v>
       </c>
       <c r="M12" t="n">
-        <v>3.78328275245918</v>
+        <v>3.771261259498244</v>
       </c>
       <c r="N12" t="n">
-        <v>23.17693681948478</v>
+        <v>23.04221708351595</v>
       </c>
       <c r="O12" t="n">
-        <v>4.814243120105671</v>
+        <v>4.800230940643996</v>
       </c>
       <c r="P12" t="n">
-        <v>346.5374321319877</v>
+        <v>346.5814584312064</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -33063,28 +33318,28 @@
         <v>0.0834</v>
       </c>
       <c r="I13" t="n">
-        <v>0.7939212853640598</v>
+        <v>0.789920917023893</v>
       </c>
       <c r="J13" t="n">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="K13" t="n">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="L13" t="n">
-        <v>0.5577600691927389</v>
+        <v>0.5589378910168973</v>
       </c>
       <c r="M13" t="n">
-        <v>4.08055849944023</v>
+        <v>4.068213102618934</v>
       </c>
       <c r="N13" t="n">
-        <v>26.55285154711987</v>
+        <v>26.39046969096782</v>
       </c>
       <c r="O13" t="n">
-        <v>5.152945909586076</v>
+        <v>5.137165530812474</v>
       </c>
       <c r="P13" t="n">
-        <v>340.2571346323298</v>
+        <v>340.3008305833291</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -33141,28 +33396,28 @@
         <v>0.163</v>
       </c>
       <c r="I14" t="n">
-        <v>0.883564882452739</v>
+        <v>0.8778508142082304</v>
       </c>
       <c r="J14" t="n">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="K14" t="n">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="L14" t="n">
-        <v>0.6070377857601155</v>
+        <v>0.6069801857678885</v>
       </c>
       <c r="M14" t="n">
-        <v>3.916346443979021</v>
+        <v>3.912097791169459</v>
       </c>
       <c r="N14" t="n">
-        <v>26.76116884556399</v>
+        <v>26.6542305246646</v>
       </c>
       <c r="O14" t="n">
-        <v>5.173119836768136</v>
+        <v>5.16277353025141</v>
       </c>
       <c r="P14" t="n">
-        <v>334.6940830123077</v>
+        <v>334.7566719296082</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -33219,28 +33474,28 @@
         <v>0.1423</v>
       </c>
       <c r="I15" t="n">
-        <v>0.7580865401273504</v>
+        <v>0.7606758706457836</v>
       </c>
       <c r="J15" t="n">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="K15" t="n">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="L15" t="n">
-        <v>0.5362658889691796</v>
+        <v>0.5419427651138113</v>
       </c>
       <c r="M15" t="n">
-        <v>4.018519604592219</v>
+        <v>3.998435820275169</v>
       </c>
       <c r="N15" t="n">
-        <v>26.13158050672673</v>
+        <v>25.94350231349096</v>
       </c>
       <c r="O15" t="n">
-        <v>5.111905760743905</v>
+        <v>5.09347644673959</v>
       </c>
       <c r="P15" t="n">
-        <v>333.7133466401414</v>
+        <v>333.6848620423847</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -33297,28 +33552,28 @@
         <v>0.0774</v>
       </c>
       <c r="I16" t="n">
-        <v>0.6825922932993563</v>
+        <v>0.6841562607690729</v>
       </c>
       <c r="J16" t="n">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="K16" t="n">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="L16" t="n">
-        <v>0.4989399809364947</v>
+        <v>0.5041580210192254</v>
       </c>
       <c r="M16" t="n">
-        <v>3.888078788227847</v>
+        <v>3.865289139900712</v>
       </c>
       <c r="N16" t="n">
-        <v>24.60387106304076</v>
+        <v>24.42025654405979</v>
       </c>
       <c r="O16" t="n">
-        <v>4.960228932523252</v>
+        <v>4.94168559745152</v>
       </c>
       <c r="P16" t="n">
-        <v>334.1714672365325</v>
+        <v>334.1542529759328</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -33375,28 +33630,28 @@
         <v>0.1178</v>
       </c>
       <c r="I17" t="n">
-        <v>0.8285385248387811</v>
+        <v>0.8231192146294203</v>
       </c>
       <c r="J17" t="n">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="K17" t="n">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="L17" t="n">
-        <v>0.6164130714929761</v>
+        <v>0.6160300984076765</v>
       </c>
       <c r="M17" t="n">
-        <v>3.904020869607985</v>
+        <v>3.901539479402516</v>
       </c>
       <c r="N17" t="n">
-        <v>22.46242343666826</v>
+        <v>22.40184201809502</v>
       </c>
       <c r="O17" t="n">
-        <v>4.739453917559307</v>
+        <v>4.733058421158039</v>
       </c>
       <c r="P17" t="n">
-        <v>332.3128597926631</v>
+        <v>332.3724377294197</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -33453,28 +33708,28 @@
         <v>0.1043</v>
       </c>
       <c r="I18" t="n">
-        <v>0.8570180235940409</v>
+        <v>0.8584436608217576</v>
       </c>
       <c r="J18" t="n">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="K18" t="n">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="L18" t="n">
-        <v>0.6263175624859914</v>
+        <v>0.6309775209571911</v>
       </c>
       <c r="M18" t="n">
-        <v>3.922581057416161</v>
+        <v>3.897724453002616</v>
       </c>
       <c r="N18" t="n">
-        <v>23.0423752519885</v>
+        <v>22.86259537495904</v>
       </c>
       <c r="O18" t="n">
-        <v>4.800247415705622</v>
+        <v>4.781484641296993</v>
       </c>
       <c r="P18" t="n">
-        <v>325.5309460857107</v>
+        <v>325.5152683528335</v>
       </c>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr">
@@ -33531,28 +33786,28 @@
         <v>0.1026</v>
       </c>
       <c r="I19" t="n">
-        <v>1.00827238729423</v>
+        <v>1.001080814743462</v>
       </c>
       <c r="J19" t="n">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="K19" t="n">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="L19" t="n">
-        <v>0.7373384489835344</v>
+        <v>0.7361278061143157</v>
       </c>
       <c r="M19" t="n">
-        <v>3.56510579171803</v>
+        <v>3.572335292982127</v>
       </c>
       <c r="N19" t="n">
-        <v>19.04252820199344</v>
+        <v>19.05643604111386</v>
       </c>
       <c r="O19" t="n">
-        <v>4.363774536109014</v>
+        <v>4.365367801355788</v>
       </c>
       <c r="P19" t="n">
-        <v>319.5020496412056</v>
+        <v>319.5811335789024</v>
       </c>
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr">
@@ -33609,28 +33864,28 @@
         <v>0.1406</v>
       </c>
       <c r="I20" t="n">
-        <v>0.9765930098924861</v>
+        <v>0.9692904328539931</v>
       </c>
       <c r="J20" t="n">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="K20" t="n">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="L20" t="n">
-        <v>0.6544078272212521</v>
+        <v>0.6534147241973423</v>
       </c>
       <c r="M20" t="n">
-        <v>4.172732919827648</v>
+        <v>4.169710444549388</v>
       </c>
       <c r="N20" t="n">
-        <v>26.48389589517747</v>
+        <v>26.43577480864134</v>
       </c>
       <c r="O20" t="n">
-        <v>5.146250663850088</v>
+        <v>5.141573184215249</v>
       </c>
       <c r="P20" t="n">
-        <v>322.9851265305311</v>
+        <v>323.0654426857719</v>
       </c>
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr">
@@ -33687,28 +33942,28 @@
         <v>0.1091</v>
       </c>
       <c r="I21" t="n">
-        <v>0.8946456198967926</v>
+        <v>0.8899985410044076</v>
       </c>
       <c r="J21" t="n">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="K21" t="n">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="L21" t="n">
-        <v>0.5888727071397601</v>
+        <v>0.5898818076079189</v>
       </c>
       <c r="M21" t="n">
-        <v>4.362261974664419</v>
+        <v>4.351572356698926</v>
       </c>
       <c r="N21" t="n">
-        <v>29.38300432132882</v>
+        <v>29.21363651108026</v>
       </c>
       <c r="O21" t="n">
-        <v>5.420609220496236</v>
+        <v>5.404964061960103</v>
       </c>
       <c r="P21" t="n">
-        <v>332.9857486216927</v>
+        <v>333.0368527503924</v>
       </c>
       <c r="Q21" t="inlineStr"/>
       <c r="R21" t="inlineStr">
@@ -33765,28 +34020,28 @@
         <v>0.1106</v>
       </c>
       <c r="I22" t="n">
-        <v>0.8205480498133799</v>
+        <v>0.8174544508702455</v>
       </c>
       <c r="J22" t="n">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="K22" t="n">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="L22" t="n">
-        <v>0.4851104365853913</v>
+        <v>0.487219901473889</v>
       </c>
       <c r="M22" t="n">
-        <v>5.051894006400448</v>
+        <v>5.027906841060284</v>
       </c>
       <c r="N22" t="n">
-        <v>37.5768821590568</v>
+        <v>37.30751027246771</v>
       </c>
       <c r="O22" t="n">
-        <v>6.129998544784232</v>
+        <v>6.107987415873391</v>
       </c>
       <c r="P22" t="n">
-        <v>332.0382820402002</v>
+        <v>332.0722953932639</v>
       </c>
       <c r="Q22" t="inlineStr"/>
       <c r="R22" t="inlineStr">
@@ -33824,7 +34079,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W370"/>
+  <dimension ref="A1:W373"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -77077,6 +77332,357 @@
         </is>
       </c>
     </row>
+    <row r="371">
+      <c r="A371" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-07 22:26:48+00:00</t>
+        </is>
+      </c>
+      <c r="B371" t="inlineStr">
+        <is>
+          <t>-44.15775823151844,168.2438727088471</t>
+        </is>
+      </c>
+      <c r="C371" t="inlineStr">
+        <is>
+          <t>-44.15771175376633,168.24483698321478</t>
+        </is>
+      </c>
+      <c r="D371" t="inlineStr">
+        <is>
+          <t>-44.15743135847851,168.2456450230895</t>
+        </is>
+      </c>
+      <c r="E371" t="inlineStr">
+        <is>
+          <t>-44.1570412470177,168.24637177823155</t>
+        </is>
+      </c>
+      <c r="F371" t="inlineStr">
+        <is>
+          <t>-44.15662116480408,168.24702936275483</t>
+        </is>
+      </c>
+      <c r="G371" t="inlineStr">
+        <is>
+          <t>-44.156193304760414,168.24767568072997</t>
+        </is>
+      </c>
+      <c r="H371" t="inlineStr">
+        <is>
+          <t>-44.15576712575136,168.24834994381456</t>
+        </is>
+      </c>
+      <c r="I371" t="inlineStr">
+        <is>
+          <t>-44.15537227801902,168.24905912723972</t>
+        </is>
+      </c>
+      <c r="J371" t="inlineStr">
+        <is>
+          <t>-44.154928638309656,168.24971393804438</t>
+        </is>
+      </c>
+      <c r="K371" t="inlineStr">
+        <is>
+          <t>-44.15451941970136,168.25039014476693</t>
+        </is>
+      </c>
+      <c r="L371" t="inlineStr">
+        <is>
+          <t>-44.15409719368002,168.2510162132404</t>
+        </is>
+      </c>
+      <c r="M371" t="inlineStr">
+        <is>
+          <t>-44.15361215715936,168.25157839980798</t>
+        </is>
+      </c>
+      <c r="N371" t="inlineStr">
+        <is>
+          <t>-44.153113860494436,168.2521475781415</t>
+        </is>
+      </c>
+      <c r="O371" t="inlineStr">
+        <is>
+          <t>-44.15257990660647,168.25265248066938</t>
+        </is>
+      </c>
+      <c r="P371" t="inlineStr">
+        <is>
+          <t>-44.1520708497063,168.25320227699416</t>
+        </is>
+      </c>
+      <c r="Q371" t="inlineStr">
+        <is>
+          <t>-44.151563713976955,168.2537451743471</t>
+        </is>
+      </c>
+      <c r="R371" t="inlineStr">
+        <is>
+          <t>-44.15098663927979,168.25411943343232</t>
+        </is>
+      </c>
+      <c r="S371" t="inlineStr">
+        <is>
+          <t>-44.1504234105114,168.25455629456013</t>
+        </is>
+      </c>
+      <c r="T371" t="inlineStr">
+        <is>
+          <t>-44.14981625148497,168.25486535615627</t>
+        </is>
+      </c>
+      <c r="U371" t="inlineStr">
+        <is>
+          <t>-44.14919429945831,168.25510682464883</t>
+        </is>
+      </c>
+      <c r="V371" t="inlineStr">
+        <is>
+          <t>-44.14858445902069,168.2553359296321</t>
+        </is>
+      </c>
+      <c r="W371" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="372">
+      <c r="A372" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-15 22:26:35+00:00</t>
+        </is>
+      </c>
+      <c r="B372" t="inlineStr">
+        <is>
+          <t>-44.15774592015168,168.24386448599677</t>
+        </is>
+      </c>
+      <c r="C372" t="inlineStr">
+        <is>
+          <t>-44.15770195330406,168.24483043727565</t>
+        </is>
+      </c>
+      <c r="D372" t="inlineStr">
+        <is>
+          <t>-44.157416941308675,168.24563539342708</t>
+        </is>
+      </c>
+      <c r="E372" t="inlineStr">
+        <is>
+          <t>-44.157035069437235,168.24636717577167</t>
+        </is>
+      </c>
+      <c r="F372" t="inlineStr">
+        <is>
+          <t>-44.15662271538184,168.2470308573162</t>
+        </is>
+      </c>
+      <c r="G372" t="inlineStr">
+        <is>
+          <t>-44.15619134197061,168.2476734933299</t>
+        </is>
+      </c>
+      <c r="H372" t="inlineStr">
+        <is>
+          <t>-44.1557656536652,168.24834830326338</t>
+        </is>
+      </c>
+      <c r="I372" t="inlineStr">
+        <is>
+          <t>-44.15536961425607,168.24905615861823</t>
+        </is>
+      </c>
+      <c r="J372" t="inlineStr">
+        <is>
+          <t>-44.154929479494534,168.24971487550394</t>
+        </is>
+      </c>
+      <c r="K372" t="inlineStr">
+        <is>
+          <t>-44.15451496161801,168.25038471002782</t>
+        </is>
+      </c>
+      <c r="L372" t="inlineStr">
+        <is>
+          <t>-44.15409533373144,168.25101333208607</t>
+        </is>
+      </c>
+      <c r="M372" t="inlineStr">
+        <is>
+          <t>-44.153606891535354,168.25156890674978</t>
+        </is>
+      </c>
+      <c r="N372" t="inlineStr">
+        <is>
+          <t>-44.15310821095515,168.25213739292093</t>
+        </is>
+      </c>
+      <c r="O372" t="inlineStr">
+        <is>
+          <t>-44.15257924841139,168.25265129404775</t>
+        </is>
+      </c>
+      <c r="P372" t="inlineStr">
+        <is>
+          <t>-44.152063774152474,168.25318952086724</t>
+        </is>
+      </c>
+      <c r="Q372" t="inlineStr">
+        <is>
+          <t>-44.15156100747813,168.25373928087956</t>
+        </is>
+      </c>
+      <c r="R372" t="inlineStr">
+        <is>
+          <t>-44.15098814445629,168.2541236912445</t>
+        </is>
+      </c>
+      <c r="S372" t="inlineStr">
+        <is>
+          <t>-44.15042484699064,168.2545605978673</t>
+        </is>
+      </c>
+      <c r="T372" t="inlineStr">
+        <is>
+          <t>-44.1498179525684,168.2548704521337</t>
+        </is>
+      </c>
+      <c r="U372" t="inlineStr">
+        <is>
+          <t>-44.149192619996704,168.25510050076605</t>
+        </is>
+      </c>
+      <c r="V372" t="inlineStr">
+        <is>
+          <t>-44.14858274519371,168.25532739305012</t>
+        </is>
+      </c>
+      <c r="W372" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="373">
+      <c r="A373" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-23 22:26:42+00:00</t>
+        </is>
+      </c>
+      <c r="B373" t="inlineStr">
+        <is>
+          <t>-44.15770955301955,168.24384019614877</t>
+        </is>
+      </c>
+      <c r="C373" t="inlineStr">
+        <is>
+          <t>-44.157692881801545,168.2448243782264</t>
+        </is>
+      </c>
+      <c r="D373" t="inlineStr">
+        <is>
+          <t>-44.157414025476506,168.24563344585542</t>
+        </is>
+      </c>
+      <c r="E373" t="inlineStr">
+        <is>
+          <t>-44.15703522783673,168.24636729378346</t>
+        </is>
+      </c>
+      <c r="F373" t="inlineStr">
+        <is>
+          <t>-44.15663179733698,168.24703961117694</t>
+        </is>
+      </c>
+      <c r="G373" t="inlineStr">
+        <is>
+          <t>-44.15618888848328,168.24767075908005</t>
+        </is>
+      </c>
+      <c r="H373" t="inlineStr">
+        <is>
+          <t>-44.155768527738154,168.24835150624435</t>
+        </is>
+      </c>
+      <c r="I373" t="inlineStr">
+        <is>
+          <t>-44.15536723088917,168.24905350248343</t>
+        </is>
+      </c>
+      <c r="J373" t="inlineStr">
+        <is>
+          <t>-44.15492821771721,168.2497134693146</t>
+        </is>
+      </c>
+      <c r="K373" t="inlineStr">
+        <is>
+          <t>-44.15451442124425,168.25038405127165</t>
+        </is>
+      </c>
+      <c r="L373" t="inlineStr">
+        <is>
+          <t>-44.15409215381919,168.251008406242</t>
+        </is>
+      </c>
+      <c r="M373" t="inlineStr">
+        <is>
+          <t>-44.15361034710119,168.25157513656904</t>
+        </is>
+      </c>
+      <c r="N373" t="inlineStr">
+        <is>
+          <t>-44.15310140956694,168.25212513110463</t>
+        </is>
+      </c>
+      <c r="O373" t="inlineStr">
+        <is>
+          <t>-44.15257310525689,168.25264021891357</t>
+        </is>
+      </c>
+      <c r="P373" t="inlineStr">
+        <is>
+          <t>-44.15205757618566,168.2531783468981</t>
+        </is>
+      </c>
+      <c r="Q373" t="inlineStr">
+        <is>
+          <t>-44.15154273860371,168.2536994999882</t>
+        </is>
+      </c>
+      <c r="R373" t="inlineStr">
+        <is>
+          <t>-44.15098762952751,168.25412223462453</t>
+        </is>
+      </c>
+      <c r="S373" t="inlineStr">
+        <is>
+          <t>-44.15041664393614,168.2545360237214</t>
+        </is>
+      </c>
+      <c r="T373" t="inlineStr">
+        <is>
+          <t>-44.14981708312578,168.25486784752297</t>
+        </is>
+      </c>
+      <c r="U373" t="inlineStr">
+        <is>
+          <t>-44.14919140705201,168.25509593351765</t>
+        </is>
+      </c>
+      <c r="V373" t="inlineStr">
+        <is>
+          <t>-44.148579896860184,168.25531320549257</t>
+        </is>
+      </c>
+      <c r="W373" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0455/nzd0455.xlsx
+++ b/data/nzd0455/nzd0455.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W373"/>
+  <dimension ref="A1:W374"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -28425,6 +28425,81 @@
       <c r="W373" t="inlineStr">
         <is>
           <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="374">
+      <c r="A374" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-19 22:26:21+00:00</t>
+        </is>
+      </c>
+      <c r="B374" t="n">
+        <v>385.54</v>
+      </c>
+      <c r="C374" t="n">
+        <v>350.76</v>
+      </c>
+      <c r="D374" t="n">
+        <v>348.83</v>
+      </c>
+      <c r="E374" t="n">
+        <v>358.19</v>
+      </c>
+      <c r="F374" t="n">
+        <v>365.89</v>
+      </c>
+      <c r="G374" t="n">
+        <v>369.99</v>
+      </c>
+      <c r="H374" t="n">
+        <v>369.48</v>
+      </c>
+      <c r="I374" t="n">
+        <v>366.9</v>
+      </c>
+      <c r="J374" t="n">
+        <v>368.66</v>
+      </c>
+      <c r="K374" t="n">
+        <v>368.38</v>
+      </c>
+      <c r="L374" t="n">
+        <v>365.45</v>
+      </c>
+      <c r="M374" t="n">
+        <v>359.73</v>
+      </c>
+      <c r="N374" t="n">
+        <v>356.27</v>
+      </c>
+      <c r="O374" t="n">
+        <v>356.23</v>
+      </c>
+      <c r="P374" t="n">
+        <v>355.05</v>
+      </c>
+      <c r="Q374" t="n">
+        <v>354.07</v>
+      </c>
+      <c r="R374" t="n">
+        <v>349.17</v>
+      </c>
+      <c r="S374" t="n">
+        <v>343.57</v>
+      </c>
+      <c r="T374" t="n">
+        <v>344.71</v>
+      </c>
+      <c r="U374" t="n">
+        <v>354.7</v>
+      </c>
+      <c r="V374" t="n">
+        <v>353.55</v>
+      </c>
+      <c r="W374" t="inlineStr">
+        <is>
+          <t>L8</t>
         </is>
       </c>
     </row>
@@ -28439,7 +28514,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B385"/>
+  <dimension ref="A1:B386"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -32292,6 +32367,16 @@
       </c>
       <c r="B385" t="n">
         <v>-0.76</v>
+      </c>
+    </row>
+    <row r="386">
+      <c r="A386" t="inlineStr">
+        <is>
+          <t>2026-03-19 22:30:00+00:00</t>
+        </is>
+      </c>
+      <c r="B386" t="n">
+        <v>0.89</v>
       </c>
     </row>
   </sheetData>
@@ -32460,28 +32545,28 @@
         <v>0.0326</v>
       </c>
       <c r="I2" t="n">
-        <v>0.2486622145863311</v>
+        <v>0.2494681484038454</v>
       </c>
       <c r="J2" t="n">
+        <v>373</v>
+      </c>
+      <c r="K2" t="n">
         <v>372</v>
       </c>
-      <c r="K2" t="n">
-        <v>371</v>
-      </c>
       <c r="L2" t="n">
-        <v>0.02693472608936698</v>
+        <v>0.02725119132691289</v>
       </c>
       <c r="M2" t="n">
-        <v>7.84835582331841</v>
+        <v>7.830716160368368</v>
       </c>
       <c r="N2" t="n">
-        <v>119.3256448633128</v>
+        <v>119.0110882068542</v>
       </c>
       <c r="O2" t="n">
-        <v>10.92362782519218</v>
+        <v>10.90922032992524</v>
       </c>
       <c r="P2" t="n">
-        <v>377.3940410283958</v>
+        <v>377.3851773105765</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -32538,28 +32623,28 @@
         <v>0.08740000000000001</v>
       </c>
       <c r="I3" t="n">
-        <v>0.4629810356600254</v>
+        <v>0.4614263164271988</v>
       </c>
       <c r="J3" t="n">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="K3" t="n">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="L3" t="n">
-        <v>0.2545884342201895</v>
+        <v>0.2542404109846286</v>
       </c>
       <c r="M3" t="n">
-        <v>4.449649267016144</v>
+        <v>4.444935269345186</v>
       </c>
       <c r="N3" t="n">
-        <v>33.63779773972621</v>
+        <v>33.57081875252432</v>
       </c>
       <c r="O3" t="n">
-        <v>5.799810146869138</v>
+        <v>5.794033029982167</v>
       </c>
       <c r="P3" t="n">
-        <v>341.396587915179</v>
+        <v>341.4136364805746</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -32616,28 +32701,28 @@
         <v>0.07199999999999999</v>
       </c>
       <c r="I4" t="n">
-        <v>0.7320081421659598</v>
+        <v>0.7289980657313475</v>
       </c>
       <c r="J4" t="n">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="K4" t="n">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="L4" t="n">
-        <v>0.4324649578139742</v>
+        <v>0.4312459767907023</v>
       </c>
       <c r="M4" t="n">
-        <v>4.788440487961488</v>
+        <v>4.789835770809914</v>
       </c>
       <c r="N4" t="n">
-        <v>37.68923101936049</v>
+        <v>37.67516182736821</v>
       </c>
       <c r="O4" t="n">
-        <v>6.13915556240111</v>
+        <v>6.138009598181499</v>
       </c>
       <c r="P4" t="n">
-        <v>335.0691995106314</v>
+        <v>335.1022070684321</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -32694,28 +32779,28 @@
         <v>0.0653</v>
       </c>
       <c r="I5" t="n">
-        <v>0.7495379115994859</v>
+        <v>0.7477239516072879</v>
       </c>
       <c r="J5" t="n">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="K5" t="n">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="L5" t="n">
-        <v>0.4959911535511148</v>
+        <v>0.4959170374135757</v>
       </c>
       <c r="M5" t="n">
-        <v>4.228862920609981</v>
+        <v>4.225948089173079</v>
       </c>
       <c r="N5" t="n">
-        <v>30.5981473197931</v>
+        <v>30.54770051949574</v>
       </c>
       <c r="O5" t="n">
-        <v>5.531559212355328</v>
+        <v>5.526997423510865</v>
       </c>
       <c r="P5" t="n">
-        <v>341.6877803727527</v>
+        <v>341.707671691326</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -32772,28 +32857,28 @@
         <v>0.07149999999999999</v>
       </c>
       <c r="I6" t="n">
-        <v>0.7922414993885674</v>
+        <v>0.7913535258575098</v>
       </c>
       <c r="J6" t="n">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="K6" t="n">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="L6" t="n">
-        <v>0.4675942131305895</v>
+        <v>0.4683767559835398</v>
       </c>
       <c r="M6" t="n">
-        <v>4.567294639713853</v>
+        <v>4.559137970759962</v>
       </c>
       <c r="N6" t="n">
-        <v>38.30297520167677</v>
+        <v>38.20785521731468</v>
       </c>
       <c r="O6" t="n">
-        <v>6.188939747782069</v>
+        <v>6.181250295637176</v>
       </c>
       <c r="P6" t="n">
-        <v>346.4963684320909</v>
+        <v>346.5061056724197</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -32850,28 +32935,28 @@
         <v>0.0478</v>
       </c>
       <c r="I7" t="n">
-        <v>0.6388959758891245</v>
+        <v>0.6368468607130029</v>
       </c>
       <c r="J7" t="n">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="K7" t="n">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="L7" t="n">
-        <v>0.4839359370222082</v>
+        <v>0.4832937475888494</v>
       </c>
       <c r="M7" t="n">
-        <v>3.682059759560806</v>
+        <v>3.680347314026896</v>
       </c>
       <c r="N7" t="n">
-        <v>23.3302688001786</v>
+        <v>23.30802707424643</v>
       </c>
       <c r="O7" t="n">
-        <v>4.830141695662623</v>
+        <v>4.827838758103509</v>
       </c>
       <c r="P7" t="n">
-        <v>356.8800942817863</v>
+        <v>356.9025642386414</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -32928,28 +33013,28 @@
         <v>0.07240000000000001</v>
       </c>
       <c r="I8" t="n">
-        <v>0.6425580921972022</v>
+        <v>0.6412161691386183</v>
       </c>
       <c r="J8" t="n">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="K8" t="n">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="L8" t="n">
-        <v>0.4357750412572063</v>
+        <v>0.4359713057766741</v>
       </c>
       <c r="M8" t="n">
-        <v>4.113967627212819</v>
+        <v>4.108588049324516</v>
       </c>
       <c r="N8" t="n">
-        <v>28.65223003666696</v>
+        <v>28.59270027642397</v>
       </c>
       <c r="O8" t="n">
-        <v>5.352777786968833</v>
+        <v>5.347214253835727</v>
       </c>
       <c r="P8" t="n">
-        <v>354.9267067643892</v>
+        <v>354.9414218734179</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -33006,28 +33091,28 @@
         <v>0.0708</v>
       </c>
       <c r="I9" t="n">
-        <v>0.7595851151147518</v>
+        <v>0.7590218189748016</v>
       </c>
       <c r="J9" t="n">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="K9" t="n">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="L9" t="n">
-        <v>0.5518878473282277</v>
+        <v>0.5528716223368928</v>
       </c>
       <c r="M9" t="n">
-        <v>3.884204707666886</v>
+        <v>3.876501924715162</v>
       </c>
       <c r="N9" t="n">
-        <v>25.10917689139512</v>
+        <v>25.0449059206123</v>
       </c>
       <c r="O9" t="n">
-        <v>5.010905795501959</v>
+        <v>5.004488577328587</v>
       </c>
       <c r="P9" t="n">
-        <v>347.7573986580551</v>
+        <v>347.7635755875458</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -33084,28 +33169,28 @@
         <v>0.0804</v>
       </c>
       <c r="I10" t="n">
-        <v>0.6298959937002301</v>
+        <v>0.6316618004575615</v>
       </c>
       <c r="J10" t="n">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="K10" t="n">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="L10" t="n">
-        <v>0.4699079153433245</v>
+        <v>0.472382809224571</v>
       </c>
       <c r="M10" t="n">
-        <v>3.777570373029868</v>
+        <v>3.775822439456476</v>
       </c>
       <c r="N10" t="n">
-        <v>23.98943087651378</v>
+        <v>23.95504712633246</v>
       </c>
       <c r="O10" t="n">
-        <v>4.897900660131214</v>
+        <v>4.894389351730455</v>
       </c>
       <c r="P10" t="n">
-        <v>348.5376766703165</v>
+        <v>348.5183133850733</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -33162,28 +33247,28 @@
         <v>0.0702</v>
       </c>
       <c r="I11" t="n">
-        <v>0.5069051360762543</v>
+        <v>0.5082937869408349</v>
       </c>
       <c r="J11" t="n">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="K11" t="n">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="L11" t="n">
-        <v>0.3850304503379364</v>
+        <v>0.3874513188465376</v>
       </c>
       <c r="M11" t="n">
-        <v>3.571009177006828</v>
+        <v>3.568300685843815</v>
       </c>
       <c r="N11" t="n">
-        <v>21.99660276003265</v>
+        <v>21.95614130500216</v>
       </c>
       <c r="O11" t="n">
-        <v>4.69005359884433</v>
+        <v>4.685738074732962</v>
       </c>
       <c r="P11" t="n">
-        <v>352.2550958950198</v>
+        <v>352.2398683834687</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -33240,28 +33325,28 @@
         <v>0.0683</v>
       </c>
       <c r="I12" t="n">
-        <v>0.7612515732009105</v>
+        <v>0.7605218693010267</v>
       </c>
       <c r="J12" t="n">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="K12" t="n">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="L12" t="n">
-        <v>0.5740977082779773</v>
+        <v>0.5749395048302759</v>
       </c>
       <c r="M12" t="n">
-        <v>3.771261259498244</v>
+        <v>3.764457759984214</v>
       </c>
       <c r="N12" t="n">
-        <v>23.04221708351595</v>
+        <v>22.98555297871756</v>
       </c>
       <c r="O12" t="n">
-        <v>4.800230940643996</v>
+        <v>4.794325080625798</v>
       </c>
       <c r="P12" t="n">
-        <v>346.5814584312064</v>
+        <v>346.589460136205</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -33318,28 +33403,28 @@
         <v>0.0834</v>
       </c>
       <c r="I13" t="n">
-        <v>0.789920917023893</v>
+        <v>0.7890853181842277</v>
       </c>
       <c r="J13" t="n">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="K13" t="n">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="L13" t="n">
-        <v>0.5589378910168973</v>
+        <v>0.5597297591435426</v>
       </c>
       <c r="M13" t="n">
-        <v>4.068213102618934</v>
+        <v>4.061554713565796</v>
       </c>
       <c r="N13" t="n">
-        <v>26.39046969096782</v>
+        <v>26.32642018190262</v>
       </c>
       <c r="O13" t="n">
-        <v>5.137165530812474</v>
+        <v>5.130927809071438</v>
       </c>
       <c r="P13" t="n">
-        <v>340.3008305833291</v>
+        <v>340.3099934991545</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -33396,28 +33481,28 @@
         <v>0.163</v>
       </c>
       <c r="I14" t="n">
-        <v>0.8778508142082304</v>
+        <v>0.8768768333400245</v>
       </c>
       <c r="J14" t="n">
+        <v>373</v>
+      </c>
+      <c r="K14" t="n">
         <v>372</v>
       </c>
-      <c r="K14" t="n">
-        <v>371</v>
-      </c>
       <c r="L14" t="n">
-        <v>0.6069801857678885</v>
+        <v>0.6077016298316247</v>
       </c>
       <c r="M14" t="n">
-        <v>3.912097791169459</v>
+        <v>3.906255407641249</v>
       </c>
       <c r="N14" t="n">
-        <v>26.6542305246646</v>
+        <v>26.5916508449313</v>
       </c>
       <c r="O14" t="n">
-        <v>5.16277353025141</v>
+        <v>5.15670930390024</v>
       </c>
       <c r="P14" t="n">
-        <v>334.7566719296082</v>
+        <v>334.767383840921</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -33474,28 +33559,28 @@
         <v>0.1423</v>
       </c>
       <c r="I15" t="n">
-        <v>0.7606758706457836</v>
+        <v>0.7618976823419941</v>
       </c>
       <c r="J15" t="n">
+        <v>373</v>
+      </c>
+      <c r="K15" t="n">
         <v>372</v>
       </c>
-      <c r="K15" t="n">
-        <v>371</v>
-      </c>
       <c r="L15" t="n">
-        <v>0.5419427651138113</v>
+        <v>0.5439963504251603</v>
       </c>
       <c r="M15" t="n">
-        <v>3.998435820275169</v>
+        <v>3.993476935951958</v>
       </c>
       <c r="N15" t="n">
-        <v>25.94350231349096</v>
+        <v>25.88787670034578</v>
       </c>
       <c r="O15" t="n">
-        <v>5.09347644673959</v>
+        <v>5.088013040504689</v>
       </c>
       <c r="P15" t="n">
-        <v>333.6848620423847</v>
+        <v>333.6713728338823</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -33552,28 +33637,28 @@
         <v>0.0774</v>
       </c>
       <c r="I16" t="n">
-        <v>0.6841562607690729</v>
+        <v>0.6855823563952649</v>
       </c>
       <c r="J16" t="n">
+        <v>373</v>
+      </c>
+      <c r="K16" t="n">
         <v>372</v>
       </c>
-      <c r="K16" t="n">
-        <v>371</v>
-      </c>
       <c r="L16" t="n">
-        <v>0.5041580210192254</v>
+        <v>0.5064043469534341</v>
       </c>
       <c r="M16" t="n">
-        <v>3.865289139900712</v>
+        <v>3.861533396140386</v>
       </c>
       <c r="N16" t="n">
-        <v>24.42025654405979</v>
+        <v>24.37384024414471</v>
       </c>
       <c r="O16" t="n">
-        <v>4.94168559745152</v>
+        <v>4.93698696009466</v>
       </c>
       <c r="P16" t="n">
-        <v>334.1542529759328</v>
+        <v>334.1385084047311</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -33630,28 +33715,28 @@
         <v>0.1178</v>
       </c>
       <c r="I17" t="n">
-        <v>0.8231192146294203</v>
+        <v>0.8230091863368182</v>
       </c>
       <c r="J17" t="n">
+        <v>373</v>
+      </c>
+      <c r="K17" t="n">
         <v>372</v>
       </c>
-      <c r="K17" t="n">
-        <v>371</v>
-      </c>
       <c r="L17" t="n">
-        <v>0.6160300984076765</v>
+        <v>0.6172920689337271</v>
       </c>
       <c r="M17" t="n">
-        <v>3.901539479402516</v>
+        <v>3.891635437904335</v>
       </c>
       <c r="N17" t="n">
-        <v>22.40184201809502</v>
+        <v>22.34173647974774</v>
       </c>
       <c r="O17" t="n">
-        <v>4.733058421158039</v>
+        <v>4.726704611010481</v>
       </c>
       <c r="P17" t="n">
-        <v>332.3724377294197</v>
+        <v>332.3736524784557</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -33708,28 +33793,28 @@
         <v>0.1043</v>
       </c>
       <c r="I18" t="n">
-        <v>0.8584436608217576</v>
+        <v>0.8588760763542466</v>
       </c>
       <c r="J18" t="n">
+        <v>373</v>
+      </c>
+      <c r="K18" t="n">
         <v>372</v>
       </c>
-      <c r="K18" t="n">
-        <v>371</v>
-      </c>
       <c r="L18" t="n">
-        <v>0.6309775209571911</v>
+        <v>0.6324991683132717</v>
       </c>
       <c r="M18" t="n">
-        <v>3.897724453002616</v>
+        <v>3.889319039505806</v>
       </c>
       <c r="N18" t="n">
-        <v>22.86259537495904</v>
+        <v>22.80290475331966</v>
       </c>
       <c r="O18" t="n">
-        <v>4.781484641296993</v>
+        <v>4.775238711658262</v>
       </c>
       <c r="P18" t="n">
-        <v>325.5152683528335</v>
+        <v>325.5104943411789</v>
       </c>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr">
@@ -33786,28 +33871,28 @@
         <v>0.1026</v>
       </c>
       <c r="I19" t="n">
-        <v>1.001080814743462</v>
+        <v>0.9996727215783408</v>
       </c>
       <c r="J19" t="n">
+        <v>373</v>
+      </c>
+      <c r="K19" t="n">
         <v>372</v>
       </c>
-      <c r="K19" t="n">
-        <v>371</v>
-      </c>
       <c r="L19" t="n">
-        <v>0.7361278061143157</v>
+        <v>0.736479224395422</v>
       </c>
       <c r="M19" t="n">
-        <v>3.572335292982127</v>
+        <v>3.569772458182797</v>
       </c>
       <c r="N19" t="n">
-        <v>19.05643604111386</v>
+        <v>19.02395618552006</v>
       </c>
       <c r="O19" t="n">
-        <v>4.365367801355788</v>
+        <v>4.361646040833673</v>
       </c>
       <c r="P19" t="n">
-        <v>319.5811335789024</v>
+        <v>319.5966793969315</v>
       </c>
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr">
@@ -33864,28 +33949,28 @@
         <v>0.1406</v>
       </c>
       <c r="I20" t="n">
-        <v>0.9692904328539931</v>
+        <v>0.9670849779152998</v>
       </c>
       <c r="J20" t="n">
+        <v>373</v>
+      </c>
+      <c r="K20" t="n">
         <v>372</v>
       </c>
-      <c r="K20" t="n">
-        <v>371</v>
-      </c>
       <c r="L20" t="n">
-        <v>0.6534147241973423</v>
+        <v>0.6532589630060097</v>
       </c>
       <c r="M20" t="n">
-        <v>4.169710444549388</v>
+        <v>4.167731286260413</v>
       </c>
       <c r="N20" t="n">
-        <v>26.43577480864134</v>
+        <v>26.41070140788925</v>
       </c>
       <c r="O20" t="n">
-        <v>5.141573184215249</v>
+        <v>5.139134305297853</v>
       </c>
       <c r="P20" t="n">
-        <v>323.0654426857719</v>
+        <v>323.0897916436374</v>
       </c>
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr">
@@ -33942,28 +34027,28 @@
         <v>0.1091</v>
       </c>
       <c r="I21" t="n">
-        <v>0.8899985410044076</v>
+        <v>0.8889263623843008</v>
       </c>
       <c r="J21" t="n">
+        <v>373</v>
+      </c>
+      <c r="K21" t="n">
         <v>372</v>
       </c>
-      <c r="K21" t="n">
-        <v>371</v>
-      </c>
       <c r="L21" t="n">
-        <v>0.5898818076079189</v>
+        <v>0.5905655810283674</v>
       </c>
       <c r="M21" t="n">
-        <v>4.351572356698926</v>
+        <v>4.345481889982028</v>
       </c>
       <c r="N21" t="n">
-        <v>29.21363651108026</v>
+        <v>29.14597464421808</v>
       </c>
       <c r="O21" t="n">
-        <v>5.404964061960103</v>
+        <v>5.398701199753333</v>
       </c>
       <c r="P21" t="n">
-        <v>333.0368527503924</v>
+        <v>333.048689959844</v>
       </c>
       <c r="Q21" t="inlineStr"/>
       <c r="R21" t="inlineStr">
@@ -34020,28 +34105,28 @@
         <v>0.1106</v>
       </c>
       <c r="I22" t="n">
-        <v>0.8174544508702455</v>
+        <v>0.817306546926773</v>
       </c>
       <c r="J22" t="n">
+        <v>373</v>
+      </c>
+      <c r="K22" t="n">
         <v>372</v>
       </c>
-      <c r="K22" t="n">
-        <v>371</v>
-      </c>
       <c r="L22" t="n">
-        <v>0.487219901473889</v>
+        <v>0.4885300147268817</v>
       </c>
       <c r="M22" t="n">
-        <v>5.027906841060284</v>
+        <v>5.015192173505901</v>
       </c>
       <c r="N22" t="n">
-        <v>37.30751027246771</v>
+        <v>37.2074281048473</v>
       </c>
       <c r="O22" t="n">
-        <v>6.107987415873391</v>
+        <v>6.099789185279053</v>
       </c>
       <c r="P22" t="n">
-        <v>332.0722953932639</v>
+        <v>332.0739283021139</v>
       </c>
       <c r="Q22" t="inlineStr"/>
       <c r="R22" t="inlineStr">
@@ -34079,7 +34164,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W373"/>
+  <dimension ref="A1:W374"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -77683,6 +77768,123 @@
         </is>
       </c>
     </row>
+    <row r="374">
+      <c r="A374" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-19 22:26:21+00:00</t>
+        </is>
+      </c>
+      <c r="B374" t="inlineStr">
+        <is>
+          <t>-44.15770898604864,168.2438398174654</t>
+        </is>
+      </c>
+      <c r="C374" t="inlineStr">
+        <is>
+          <t>-44.1576891560058,168.24482188968884</t>
+        </is>
+      </c>
+      <c r="D374" t="inlineStr">
+        <is>
+          <t>-44.15740325309629,168.24562625066184</t>
+        </is>
+      </c>
+      <c r="E374" t="inlineStr">
+        <is>
+          <t>-44.157028020659325,168.2463619242481</t>
+        </is>
+      </c>
+      <c r="F374" t="inlineStr">
+        <is>
+          <t>-44.1566292868779,168.2470371914103</t>
+        </is>
+      </c>
+      <c r="G374" t="inlineStr">
+        <is>
+          <t>-44.15618580409914,168.24766732173768</t>
+        </is>
+      </c>
+      <c r="H374" t="inlineStr">
+        <is>
+          <t>-44.15576698555268,168.2483497875716</t>
+        </is>
+      </c>
+      <c r="I374" t="inlineStr">
+        <is>
+          <t>-44.155362674452284,168.24904842457923</t>
+        </is>
+      </c>
+      <c r="J374" t="inlineStr">
+        <is>
+          <t>-44.15492793732226,168.24971315682808</t>
+        </is>
+      </c>
+      <c r="K374" t="inlineStr">
+        <is>
+          <t>-44.15451340804344,168.25038281610378</t>
+        </is>
+      </c>
+      <c r="L374" t="inlineStr">
+        <is>
+          <t>-44.154087893936435,168.2510018074706</t>
+        </is>
+      </c>
+      <c r="M374" t="inlineStr">
+        <is>
+          <t>-44.15360458782463,168.2515647535374</t>
+        </is>
+      </c>
+      <c r="N374" t="inlineStr">
+        <is>
+          <t>-44.15309822827206,168.2521193957399</t>
+        </is>
+      </c>
+      <c r="O374" t="inlineStr">
+        <is>
+          <t>-44.15257310525689,168.25264021891357</t>
+        </is>
+      </c>
+      <c r="P374" t="inlineStr">
+        <is>
+          <t>-44.152054230380145,168.25317231493347</t>
+        </is>
+      </c>
+      <c r="Q374" t="inlineStr">
+        <is>
+          <t>-44.151540418745725,168.25369444844824</t>
+        </is>
+      </c>
+      <c r="R374" t="inlineStr">
+        <is>
+          <t>-44.15098743147796,168.25412167438608</t>
+        </is>
+      </c>
+      <c r="S374" t="inlineStr">
+        <is>
+          <t>-44.15041467822647,168.25453013498702</t>
+        </is>
+      </c>
+      <c r="T374" t="inlineStr">
+        <is>
+          <t>-44.14981557105153,168.2548633177654</t>
+        </is>
+      </c>
+      <c r="U374" t="inlineStr">
+        <is>
+          <t>-44.14918997639906,168.25509054650692</t>
+        </is>
+      </c>
+      <c r="V374" t="inlineStr">
+        <is>
+          <t>-44.1485782795853,168.25530514984612</t>
+        </is>
+      </c>
+      <c r="W374" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0455/nzd0455.xlsx
+++ b/data/nzd0455/nzd0455.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W374"/>
+  <dimension ref="A1:W377"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -28498,6 +28498,231 @@
         <v>353.55</v>
       </c>
       <c r="W374" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="375">
+      <c r="A375" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-20 22:26:06+00:00</t>
+        </is>
+      </c>
+      <c r="B375" t="n">
+        <v>384.35</v>
+      </c>
+      <c r="C375" t="n">
+        <v>354.04</v>
+      </c>
+      <c r="D375" t="n">
+        <v>352.19</v>
+      </c>
+      <c r="E375" t="n">
+        <v>359.48</v>
+      </c>
+      <c r="F375" t="n">
+        <v>366.49</v>
+      </c>
+      <c r="G375" t="n">
+        <v>369.88</v>
+      </c>
+      <c r="H375" t="n">
+        <v>370.59</v>
+      </c>
+      <c r="I375" t="n">
+        <v>368.15</v>
+      </c>
+      <c r="J375" t="n">
+        <v>370.51</v>
+      </c>
+      <c r="K375" t="n">
+        <v>370.44</v>
+      </c>
+      <c r="L375" t="n">
+        <v>367.58</v>
+      </c>
+      <c r="M375" t="n">
+        <v>363.51</v>
+      </c>
+      <c r="N375" t="n">
+        <v>361.4</v>
+      </c>
+      <c r="O375" t="n">
+        <v>358.19</v>
+      </c>
+      <c r="P375" t="n">
+        <v>355.99</v>
+      </c>
+      <c r="Q375" t="n">
+        <v>357.01</v>
+      </c>
+      <c r="R375" t="n">
+        <v>350</v>
+      </c>
+      <c r="S375" t="n">
+        <v>345.29</v>
+      </c>
+      <c r="T375" t="n">
+        <v>345.25</v>
+      </c>
+      <c r="U375" t="n">
+        <v>354.53</v>
+      </c>
+      <c r="V375" t="n">
+        <v>353.87</v>
+      </c>
+      <c r="W375" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="376">
+      <c r="A376" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-14 22:26:01+00:00</t>
+        </is>
+      </c>
+      <c r="B376" t="n">
+        <v>385.96</v>
+      </c>
+      <c r="C376" t="n">
+        <v>357.24</v>
+      </c>
+      <c r="D376" t="n">
+        <v>355.68</v>
+      </c>
+      <c r="E376" t="n">
+        <v>362.42</v>
+      </c>
+      <c r="F376" t="n">
+        <v>368.11</v>
+      </c>
+      <c r="G376" t="n">
+        <v>373.2</v>
+      </c>
+      <c r="H376" t="n">
+        <v>373.03</v>
+      </c>
+      <c r="I376" t="n">
+        <v>370.48</v>
+      </c>
+      <c r="J376" t="n">
+        <v>372.35</v>
+      </c>
+      <c r="K376" t="n">
+        <v>372.46</v>
+      </c>
+      <c r="L376" t="n">
+        <v>370.75</v>
+      </c>
+      <c r="M376" t="n">
+        <v>367.07</v>
+      </c>
+      <c r="N376" t="n">
+        <v>363.56</v>
+      </c>
+      <c r="O376" t="n">
+        <v>359.38</v>
+      </c>
+      <c r="P376" t="n">
+        <v>358.68</v>
+      </c>
+      <c r="Q376" t="n">
+        <v>358.01</v>
+      </c>
+      <c r="R376" t="n">
+        <v>351.36</v>
+      </c>
+      <c r="S376" t="n">
+        <v>347.34</v>
+      </c>
+      <c r="T376" t="n">
+        <v>347.96</v>
+      </c>
+      <c r="U376" t="n">
+        <v>356.09</v>
+      </c>
+      <c r="V376" t="n">
+        <v>355.43</v>
+      </c>
+      <c r="W376" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="377">
+      <c r="A377" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-22 22:25:40+00:00</t>
+        </is>
+      </c>
+      <c r="B377" t="n">
+        <v>390.7</v>
+      </c>
+      <c r="C377" t="n">
+        <v>357.55</v>
+      </c>
+      <c r="D377" t="n">
+        <v>355.42</v>
+      </c>
+      <c r="E377" t="n">
+        <v>362.51</v>
+      </c>
+      <c r="F377" t="n">
+        <v>367.91</v>
+      </c>
+      <c r="G377" t="n">
+        <v>373.06</v>
+      </c>
+      <c r="H377" t="n">
+        <v>373.1</v>
+      </c>
+      <c r="I377" t="n">
+        <v>371.33</v>
+      </c>
+      <c r="J377" t="n">
+        <v>372.09</v>
+      </c>
+      <c r="K377" t="n">
+        <v>373.22</v>
+      </c>
+      <c r="L377" t="n">
+        <v>370.87</v>
+      </c>
+      <c r="M377" t="n">
+        <v>367.04</v>
+      </c>
+      <c r="N377" t="n">
+        <v>364.68</v>
+      </c>
+      <c r="O377" t="n">
+        <v>360.08</v>
+      </c>
+      <c r="P377" t="n">
+        <v>358</v>
+      </c>
+      <c r="Q377" t="n">
+        <v>358.27</v>
+      </c>
+      <c r="R377" t="n">
+        <v>351.78</v>
+      </c>
+      <c r="S377" t="n">
+        <v>347.73</v>
+      </c>
+      <c r="T377" t="n">
+        <v>348.8</v>
+      </c>
+      <c r="U377" t="n">
+        <v>356.61</v>
+      </c>
+      <c r="V377" t="n">
+        <v>355.79</v>
+      </c>
+      <c r="W377" t="inlineStr">
         <is>
           <t>L8</t>
         </is>
@@ -28514,7 +28739,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B386"/>
+  <dimension ref="A1:B389"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -32377,6 +32602,36 @@
       </c>
       <c r="B386" t="n">
         <v>0.89</v>
+      </c>
+    </row>
+    <row r="387">
+      <c r="A387" t="inlineStr">
+        <is>
+          <t>2026-04-20 22:30:00+00:00</t>
+        </is>
+      </c>
+      <c r="B387" t="n">
+        <v>-0.21</v>
+      </c>
+    </row>
+    <row r="388">
+      <c r="A388" t="inlineStr">
+        <is>
+          <t>2026-05-14 22:30:00+00:00</t>
+        </is>
+      </c>
+      <c r="B388" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+    </row>
+    <row r="389">
+      <c r="A389" t="inlineStr">
+        <is>
+          <t>2026-05-22 22:30:00+00:00</t>
+        </is>
+      </c>
+      <c r="B389" t="n">
+        <v>-0.78</v>
       </c>
     </row>
   </sheetData>
@@ -32545,28 +32800,28 @@
         <v>0.0326</v>
       </c>
       <c r="I2" t="n">
-        <v>0.2494681484038454</v>
+        <v>0.254094433234254</v>
       </c>
       <c r="J2" t="n">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="K2" t="n">
-        <v>372</v>
+        <v>375</v>
       </c>
       <c r="L2" t="n">
-        <v>0.02725119132691289</v>
+        <v>0.02867848051963851</v>
       </c>
       <c r="M2" t="n">
-        <v>7.830716160368368</v>
+        <v>7.787643673909209</v>
       </c>
       <c r="N2" t="n">
-        <v>119.0110882068542</v>
+        <v>118.1845447346035</v>
       </c>
       <c r="O2" t="n">
-        <v>10.90922032992524</v>
+        <v>10.87127153255789</v>
       </c>
       <c r="P2" t="n">
-        <v>377.3851773105765</v>
+        <v>377.3339265396745</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -32623,28 +32878,28 @@
         <v>0.08740000000000001</v>
       </c>
       <c r="I3" t="n">
-        <v>0.4614263164271988</v>
+        <v>0.4653653765504301</v>
       </c>
       <c r="J3" t="n">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="K3" t="n">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="L3" t="n">
-        <v>0.2542404109846286</v>
+        <v>0.2603079581165448</v>
       </c>
       <c r="M3" t="n">
-        <v>4.444935269345186</v>
+        <v>4.430813503639088</v>
       </c>
       <c r="N3" t="n">
-        <v>33.57081875252432</v>
+        <v>33.37196700271718</v>
       </c>
       <c r="O3" t="n">
-        <v>5.794033029982167</v>
+        <v>5.776847496924008</v>
       </c>
       <c r="P3" t="n">
-        <v>341.4136364805746</v>
+        <v>341.3701383099713</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -32701,28 +32956,28 @@
         <v>0.07199999999999999</v>
       </c>
       <c r="I4" t="n">
-        <v>0.7289980657313475</v>
+        <v>0.7287329428560304</v>
       </c>
       <c r="J4" t="n">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="K4" t="n">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="L4" t="n">
-        <v>0.4312459767907023</v>
+        <v>0.4350685573169162</v>
       </c>
       <c r="M4" t="n">
-        <v>4.789835770809914</v>
+        <v>4.762808181830978</v>
       </c>
       <c r="N4" t="n">
-        <v>37.67516182736821</v>
+        <v>37.39426681663216</v>
       </c>
       <c r="O4" t="n">
-        <v>6.138009598181499</v>
+        <v>6.115085184740451</v>
       </c>
       <c r="P4" t="n">
-        <v>335.1022070684321</v>
+        <v>335.1050902246771</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -32779,28 +33034,28 @@
         <v>0.0653</v>
       </c>
       <c r="I5" t="n">
-        <v>0.7477239516072879</v>
+        <v>0.7473596715749377</v>
       </c>
       <c r="J5" t="n">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="K5" t="n">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="L5" t="n">
-        <v>0.4959170374135757</v>
+        <v>0.4997498527100807</v>
       </c>
       <c r="M5" t="n">
-        <v>4.225948089173079</v>
+        <v>4.201838639943946</v>
       </c>
       <c r="N5" t="n">
-        <v>30.54770051949574</v>
+        <v>30.31963972942805</v>
       </c>
       <c r="O5" t="n">
-        <v>5.526997423510865</v>
+        <v>5.50632724503621</v>
       </c>
       <c r="P5" t="n">
-        <v>341.707671691326</v>
+        <v>341.7116525966647</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -32857,28 +33112,28 @@
         <v>0.07149999999999999</v>
       </c>
       <c r="I6" t="n">
-        <v>0.7913535258575098</v>
+        <v>0.7910856635560165</v>
       </c>
       <c r="J6" t="n">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="K6" t="n">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="L6" t="n">
-        <v>0.4683767559835398</v>
+        <v>0.4723725518330864</v>
       </c>
       <c r="M6" t="n">
-        <v>4.559137970759962</v>
+        <v>4.527331668507967</v>
       </c>
       <c r="N6" t="n">
-        <v>38.20785521731468</v>
+        <v>37.90704425469941</v>
       </c>
       <c r="O6" t="n">
-        <v>6.181250295637176</v>
+        <v>6.156869679853505</v>
       </c>
       <c r="P6" t="n">
-        <v>346.5061056724197</v>
+        <v>346.509042646</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -32935,28 +33190,28 @@
         <v>0.0478</v>
       </c>
       <c r="I7" t="n">
-        <v>0.6368468607130029</v>
+        <v>0.6339043929338246</v>
       </c>
       <c r="J7" t="n">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="K7" t="n">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="L7" t="n">
-        <v>0.4832937475888494</v>
+        <v>0.484684732052944</v>
       </c>
       <c r="M7" t="n">
-        <v>3.680347314026896</v>
+        <v>3.66282142918858</v>
       </c>
       <c r="N7" t="n">
-        <v>23.30802707424643</v>
+        <v>23.16815027947775</v>
       </c>
       <c r="O7" t="n">
-        <v>4.827838758103509</v>
+        <v>4.813330476860877</v>
       </c>
       <c r="P7" t="n">
-        <v>356.9025642386414</v>
+        <v>356.9349842338476</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -33013,28 +33268,28 @@
         <v>0.07240000000000001</v>
       </c>
       <c r="I8" t="n">
-        <v>0.6412161691386183</v>
+        <v>0.6414520013195637</v>
       </c>
       <c r="J8" t="n">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="K8" t="n">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="L8" t="n">
-        <v>0.4359713057766741</v>
+        <v>0.4402015654675488</v>
       </c>
       <c r="M8" t="n">
-        <v>4.108588049324516</v>
+        <v>4.084994861543018</v>
       </c>
       <c r="N8" t="n">
-        <v>28.59270027642397</v>
+        <v>28.37517795119939</v>
       </c>
       <c r="O8" t="n">
-        <v>5.347214253835727</v>
+        <v>5.326835641466647</v>
       </c>
       <c r="P8" t="n">
-        <v>354.9414218734179</v>
+        <v>354.9387889719214</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -33091,28 +33346,28 @@
         <v>0.0708</v>
       </c>
       <c r="I9" t="n">
-        <v>0.7590218189748016</v>
+        <v>0.7620241969969349</v>
       </c>
       <c r="J9" t="n">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="K9" t="n">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="L9" t="n">
-        <v>0.5528716223368928</v>
+        <v>0.5585528825404928</v>
       </c>
       <c r="M9" t="n">
-        <v>3.876501924715162</v>
+        <v>3.861334585535377</v>
       </c>
       <c r="N9" t="n">
-        <v>25.0449059206123</v>
+        <v>24.88754623059834</v>
       </c>
       <c r="O9" t="n">
-        <v>5.004488577328587</v>
+        <v>4.9887419486879</v>
       </c>
       <c r="P9" t="n">
-        <v>347.7635755875458</v>
+        <v>347.7304171908328</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -33169,28 +33424,28 @@
         <v>0.0804</v>
       </c>
       <c r="I10" t="n">
-        <v>0.6316618004575615</v>
+        <v>0.6413935948429108</v>
       </c>
       <c r="J10" t="n">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="K10" t="n">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="L10" t="n">
-        <v>0.472382809224571</v>
+        <v>0.4810005355299727</v>
       </c>
       <c r="M10" t="n">
-        <v>3.775822439456476</v>
+        <v>3.791319896359511</v>
       </c>
       <c r="N10" t="n">
-        <v>23.95504712633246</v>
+        <v>24.07136703698687</v>
       </c>
       <c r="O10" t="n">
-        <v>4.894389351730455</v>
+        <v>4.906257946438086</v>
       </c>
       <c r="P10" t="n">
-        <v>348.5183133850733</v>
+        <v>348.4109338707198</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -33247,28 +33502,28 @@
         <v>0.0702</v>
       </c>
       <c r="I11" t="n">
-        <v>0.5082937869408349</v>
+        <v>0.5179787236374518</v>
       </c>
       <c r="J11" t="n">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="K11" t="n">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="L11" t="n">
-        <v>0.3874513188465376</v>
+        <v>0.3970905781170233</v>
       </c>
       <c r="M11" t="n">
-        <v>3.568300685843815</v>
+        <v>3.586942934424378</v>
       </c>
       <c r="N11" t="n">
-        <v>21.95614130500216</v>
+        <v>22.0910571135828</v>
       </c>
       <c r="O11" t="n">
-        <v>4.685738074732962</v>
+        <v>4.700112457546394</v>
       </c>
       <c r="P11" t="n">
-        <v>352.2398683834687</v>
+        <v>352.1329938797222</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -33325,28 +33580,28 @@
         <v>0.0683</v>
       </c>
       <c r="I12" t="n">
-        <v>0.7605218693010267</v>
+        <v>0.764900179989885</v>
       </c>
       <c r="J12" t="n">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="K12" t="n">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="L12" t="n">
-        <v>0.5749395048302759</v>
+        <v>0.581000646350746</v>
       </c>
       <c r="M12" t="n">
-        <v>3.764457759984214</v>
+        <v>3.758652146634762</v>
       </c>
       <c r="N12" t="n">
-        <v>22.98555297871756</v>
+        <v>22.88107536985089</v>
       </c>
       <c r="O12" t="n">
-        <v>4.794325080625798</v>
+        <v>4.783416704600477</v>
       </c>
       <c r="P12" t="n">
-        <v>346.589460136205</v>
+        <v>346.5411186242322</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -33403,28 +33658,28 @@
         <v>0.0834</v>
       </c>
       <c r="I13" t="n">
-        <v>0.7890853181842277</v>
+        <v>0.7960458821492331</v>
       </c>
       <c r="J13" t="n">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="K13" t="n">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="L13" t="n">
-        <v>0.5597297591435426</v>
+        <v>0.5665375767891314</v>
       </c>
       <c r="M13" t="n">
-        <v>4.061554713565796</v>
+        <v>4.063883380136056</v>
       </c>
       <c r="N13" t="n">
-        <v>26.32642018190262</v>
+        <v>26.29233166769133</v>
       </c>
       <c r="O13" t="n">
-        <v>5.130927809071438</v>
+        <v>5.127604866571851</v>
       </c>
       <c r="P13" t="n">
-        <v>340.3099934991545</v>
+        <v>340.2331615687226</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -33481,28 +33736,28 @@
         <v>0.163</v>
       </c>
       <c r="I14" t="n">
-        <v>0.8768768333400245</v>
+        <v>0.8846939271089149</v>
       </c>
       <c r="J14" t="n">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="K14" t="n">
-        <v>372</v>
+        <v>375</v>
       </c>
       <c r="L14" t="n">
-        <v>0.6077016298316247</v>
+        <v>0.6140526796689514</v>
       </c>
       <c r="M14" t="n">
-        <v>3.906255407641249</v>
+        <v>3.916578687396939</v>
       </c>
       <c r="N14" t="n">
-        <v>26.5916508449313</v>
+        <v>26.58716332435675</v>
       </c>
       <c r="O14" t="n">
-        <v>5.15670930390024</v>
+        <v>5.156274170790063</v>
       </c>
       <c r="P14" t="n">
-        <v>334.767383840921</v>
+        <v>334.6808559607945</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -33559,28 +33814,28 @@
         <v>0.1423</v>
       </c>
       <c r="I15" t="n">
-        <v>0.7618976823419941</v>
+        <v>0.7700286804512895</v>
       </c>
       <c r="J15" t="n">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="K15" t="n">
-        <v>372</v>
+        <v>375</v>
       </c>
       <c r="L15" t="n">
-        <v>0.5439963504251603</v>
+        <v>0.5514020918490982</v>
       </c>
       <c r="M15" t="n">
-        <v>3.993476935951958</v>
+        <v>3.99972771419594</v>
       </c>
       <c r="N15" t="n">
-        <v>25.88787670034578</v>
+        <v>25.89325749979519</v>
       </c>
       <c r="O15" t="n">
-        <v>5.088013040504689</v>
+        <v>5.088541785206759</v>
       </c>
       <c r="P15" t="n">
-        <v>333.6713728338823</v>
+        <v>333.5810466063996</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -33637,28 +33892,28 @@
         <v>0.0774</v>
       </c>
       <c r="I16" t="n">
-        <v>0.6855823563952649</v>
+        <v>0.6935779417973434</v>
       </c>
       <c r="J16" t="n">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="K16" t="n">
-        <v>372</v>
+        <v>375</v>
       </c>
       <c r="L16" t="n">
-        <v>0.5064043469534341</v>
+        <v>0.5142519583112016</v>
       </c>
       <c r="M16" t="n">
-        <v>3.861533396140386</v>
+        <v>3.867374122524847</v>
       </c>
       <c r="N16" t="n">
-        <v>24.37384024414471</v>
+        <v>24.38988219036006</v>
       </c>
       <c r="O16" t="n">
-        <v>4.93698696009466</v>
+        <v>4.938611362555274</v>
       </c>
       <c r="P16" t="n">
-        <v>334.1385084047311</v>
+        <v>334.0496793925738</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -33715,28 +33970,28 @@
         <v>0.1178</v>
       </c>
       <c r="I17" t="n">
-        <v>0.8230091863368182</v>
+        <v>0.8283261993614435</v>
       </c>
       <c r="J17" t="n">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="K17" t="n">
-        <v>372</v>
+        <v>375</v>
       </c>
       <c r="L17" t="n">
-        <v>0.6172920689337271</v>
+        <v>0.6233414005754827</v>
       </c>
       <c r="M17" t="n">
-        <v>3.891635437904335</v>
+        <v>3.885558334693678</v>
       </c>
       <c r="N17" t="n">
-        <v>22.34173647974774</v>
+        <v>22.25403485194393</v>
       </c>
       <c r="O17" t="n">
-        <v>4.726704611010481</v>
+        <v>4.71741824009107</v>
       </c>
       <c r="P17" t="n">
-        <v>332.3736524784557</v>
+        <v>332.3145857194327</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -33793,28 +34048,28 @@
         <v>0.1043</v>
       </c>
       <c r="I18" t="n">
-        <v>0.8588760763542466</v>
+        <v>0.8629169279804717</v>
       </c>
       <c r="J18" t="n">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="K18" t="n">
-        <v>372</v>
+        <v>375</v>
       </c>
       <c r="L18" t="n">
-        <v>0.6324991683132717</v>
+        <v>0.6380228622221494</v>
       </c>
       <c r="M18" t="n">
-        <v>3.889319039505806</v>
+        <v>3.877125919459257</v>
       </c>
       <c r="N18" t="n">
-        <v>22.80290475331966</v>
+        <v>22.6760252111027</v>
       </c>
       <c r="O18" t="n">
-        <v>4.775238711658262</v>
+        <v>4.761935028021981</v>
       </c>
       <c r="P18" t="n">
-        <v>325.5104943411789</v>
+        <v>325.4655949674753</v>
       </c>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr">
@@ -33871,28 +34126,28 @@
         <v>0.1026</v>
       </c>
       <c r="I19" t="n">
-        <v>0.9996727215783408</v>
+        <v>1.000381392059223</v>
       </c>
       <c r="J19" t="n">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="K19" t="n">
-        <v>372</v>
+        <v>375</v>
       </c>
       <c r="L19" t="n">
-        <v>0.736479224395422</v>
+        <v>0.7399169446600682</v>
       </c>
       <c r="M19" t="n">
-        <v>3.569772458182797</v>
+        <v>3.55012322487802</v>
       </c>
       <c r="N19" t="n">
-        <v>19.02395618552006</v>
+        <v>18.88184152258777</v>
       </c>
       <c r="O19" t="n">
-        <v>4.361646040833673</v>
+        <v>4.345324098682142</v>
       </c>
       <c r="P19" t="n">
-        <v>319.5966793969315</v>
+        <v>319.5887797341872</v>
       </c>
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr">
@@ -33949,28 +34204,28 @@
         <v>0.1406</v>
       </c>
       <c r="I20" t="n">
-        <v>0.9670849779152998</v>
+        <v>0.9645382368063357</v>
       </c>
       <c r="J20" t="n">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="K20" t="n">
-        <v>372</v>
+        <v>375</v>
       </c>
       <c r="L20" t="n">
-        <v>0.6532589630060097</v>
+        <v>0.6555607987031802</v>
       </c>
       <c r="M20" t="n">
-        <v>4.167731286260413</v>
+        <v>4.144952244656395</v>
       </c>
       <c r="N20" t="n">
-        <v>26.41070140788925</v>
+        <v>26.2375058683355</v>
       </c>
       <c r="O20" t="n">
-        <v>5.139134305297853</v>
+        <v>5.122255935458077</v>
       </c>
       <c r="P20" t="n">
-        <v>323.0897916436374</v>
+        <v>323.1180347396297</v>
       </c>
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr">
@@ -34027,28 +34282,28 @@
         <v>0.1091</v>
       </c>
       <c r="I21" t="n">
-        <v>0.8889263623843008</v>
+        <v>0.8872249940649799</v>
       </c>
       <c r="J21" t="n">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="K21" t="n">
-        <v>372</v>
+        <v>375</v>
       </c>
       <c r="L21" t="n">
-        <v>0.5905655810283674</v>
+        <v>0.5935980441016777</v>
       </c>
       <c r="M21" t="n">
-        <v>4.345481889982028</v>
+        <v>4.319451090737774</v>
       </c>
       <c r="N21" t="n">
-        <v>29.14597464421808</v>
+        <v>28.92776741401728</v>
       </c>
       <c r="O21" t="n">
-        <v>5.398701199753333</v>
+        <v>5.378453998503407</v>
       </c>
       <c r="P21" t="n">
-        <v>333.048689959844</v>
+        <v>333.0675618457884</v>
       </c>
       <c r="Q21" t="inlineStr"/>
       <c r="R21" t="inlineStr">
@@ -34105,28 +34360,28 @@
         <v>0.1106</v>
       </c>
       <c r="I22" t="n">
-        <v>0.817306546926773</v>
+        <v>0.8190313967062008</v>
       </c>
       <c r="J22" t="n">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="K22" t="n">
-        <v>372</v>
+        <v>375</v>
       </c>
       <c r="L22" t="n">
-        <v>0.4885300147268817</v>
+        <v>0.4937108348450353</v>
       </c>
       <c r="M22" t="n">
-        <v>5.015192173505901</v>
+        <v>4.983256128655134</v>
       </c>
       <c r="N22" t="n">
-        <v>37.2074281048473</v>
+        <v>36.9242029094046</v>
       </c>
       <c r="O22" t="n">
-        <v>6.099789185279053</v>
+        <v>6.076528853663463</v>
       </c>
       <c r="P22" t="n">
-        <v>332.0739283021139</v>
+        <v>332.0547491348204</v>
       </c>
       <c r="Q22" t="inlineStr"/>
       <c r="R22" t="inlineStr">
@@ -34164,7 +34419,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W374"/>
+  <dimension ref="A1:W377"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -77885,6 +78140,357 @@
         </is>
       </c>
     </row>
+    <row r="375">
+      <c r="A375" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-20 22:26:06+00:00</t>
+        </is>
+      </c>
+      <c r="B375" t="inlineStr">
+        <is>
+          <t>-44.15771862455401,168.2438462550837</t>
+        </is>
+      </c>
+      <c r="C375" t="inlineStr">
+        <is>
+          <t>-44.15766258946099,168.24480414534267</t>
+        </is>
+      </c>
+      <c r="D375" t="inlineStr">
+        <is>
+          <t>-44.157376038660495,168.24560807334174</t>
+        </is>
+      </c>
+      <c r="E375" t="inlineStr">
+        <is>
+          <t>-44.157017803891016,168.24635431249132</t>
+        </is>
+      </c>
+      <c r="F375" t="inlineStr">
+        <is>
+          <t>-44.15662485665586,168.2470329212343</t>
+        </is>
+      </c>
+      <c r="G375" t="inlineStr">
+        <is>
+          <t>-44.156186575195186,168.24766818107324</t>
+        </is>
+      </c>
+      <c r="H375" t="inlineStr">
+        <is>
+          <t>-44.15575920452562,168.24834111608774</t>
+        </is>
+      </c>
+      <c r="I375" t="inlineStr">
+        <is>
+          <t>-44.15535391207312,168.24903865938103</t>
+        </is>
+      </c>
+      <c r="J375" t="inlineStr">
+        <is>
+          <t>-44.15491496905446,168.24969870432997</t>
+        </is>
+      </c>
+      <c r="K375" t="inlineStr">
+        <is>
+          <t>-44.15449949341794,168.25036585313643</t>
+        </is>
+      </c>
+      <c r="L375" t="inlineStr">
+        <is>
+          <t>-44.15407511428615,168.2509820111621</t>
+        </is>
+      </c>
+      <c r="M375" t="inlineStr">
+        <is>
+          <t>-44.153583854421875,168.25152737464046</t>
+        </is>
+      </c>
+      <c r="N375" t="inlineStr">
+        <is>
+          <t>-44.15307009025579,168.2520686674553</t>
+        </is>
+      </c>
+      <c r="O375" t="inlineStr">
+        <is>
+          <t>-44.15256235473418,168.2526208374344</t>
+        </is>
+      </c>
+      <c r="P375" t="inlineStr">
+        <is>
+          <t>-44.15204907454813,168.25316301977622</t>
+        </is>
+      </c>
+      <c r="Q375" t="inlineStr">
+        <is>
+          <t>-44.15152620961101,168.253663507775</t>
+        </is>
+      </c>
+      <c r="R375" t="inlineStr">
+        <is>
+          <t>-44.150984143855275,168.25411237442836</t>
+        </is>
+      </c>
+      <c r="S375" t="inlineStr">
+        <is>
+          <t>-44.15040817626171,168.25451065686866</t>
+        </is>
+      </c>
+      <c r="T375" t="inlineStr">
+        <is>
+          <t>-44.14981352975103,168.254857202593</t>
+        </is>
+      </c>
+      <c r="U375" t="inlineStr">
+        <is>
+          <t>-44.14919050511865,168.25509253735868</t>
+        </is>
+      </c>
+      <c r="V375" t="inlineStr">
+        <is>
+          <t>-44.14857750715531,168.2553013023734</t>
+        </is>
+      </c>
+      <c r="W375" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="376">
+      <c r="A376" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-14 22:26:01+00:00</t>
+        </is>
+      </c>
+      <c r="B376" t="inlineStr">
+        <is>
+          <t>-44.157705584223145,168.2438375453653</t>
+        </is>
+      </c>
+      <c r="C376" t="inlineStr">
+        <is>
+          <t>-44.15763667087862,168.24478683380008</t>
+        </is>
+      </c>
+      <c r="D376" t="inlineStr">
+        <is>
+          <t>-44.15734777128284,168.24558919274935</t>
+        </is>
+      </c>
+      <c r="E376" t="inlineStr">
+        <is>
+          <t>-44.156994519161714,168.24633696477605</t>
+        </is>
+      </c>
+      <c r="F376" t="inlineStr">
+        <is>
+          <t>-44.15661289505574,168.24702139176236</t>
+        </is>
+      </c>
+      <c r="G376" t="inlineStr">
+        <is>
+          <t>-44.156163302112134,168.24764224477343</t>
+        </is>
+      </c>
+      <c r="H376" t="inlineStr">
+        <is>
+          <t>-44.15574210028398,168.24832205445549</t>
+        </is>
+      </c>
+      <c r="I376" t="inlineStr">
+        <is>
+          <t>-44.15533757899642,168.2490204570592</t>
+        </is>
+      </c>
+      <c r="J376" t="inlineStr">
+        <is>
+          <t>-44.15490207088385,168.24968432995965</t>
+        </is>
+      </c>
+      <c r="K376" t="inlineStr">
+        <is>
+          <t>-44.154485848977195,168.25034921955478</t>
+        </is>
+      </c>
+      <c r="L376" t="inlineStr">
+        <is>
+          <t>-44.154056094800914,168.25095254906643</t>
+        </is>
+      </c>
+      <c r="M376" t="inlineStr">
+        <is>
+          <t>-44.153564327714896,168.2514921712593</t>
+        </is>
+      </c>
+      <c r="N376" t="inlineStr">
+        <is>
+          <t>-44.15305824266384,168.25204730819226</t>
+        </is>
+      </c>
+      <c r="O376" t="inlineStr">
+        <is>
+          <t>-44.152555827629634,168.25260907011125</t>
+        </is>
+      </c>
+      <c r="P376" t="inlineStr">
+        <is>
+          <t>-44.15203432008888,168.25313641981404</t>
+        </is>
+      </c>
+      <c r="Q376" t="inlineStr">
+        <is>
+          <t>-44.15152137657024,168.25365298373995</t>
+        </is>
+      </c>
+      <c r="R376" t="inlineStr">
+        <is>
+          <t>-44.150978756905694,168.25409713594576</t>
+        </is>
+      </c>
+      <c r="S376" t="inlineStr">
+        <is>
+          <t>-44.150400426822856,168.25448744167528</t>
+        </is>
+      </c>
+      <c r="T376" t="inlineStr">
+        <is>
+          <t>-44.14980328544195,168.25482651349395</t>
+        </is>
+      </c>
+      <c r="U376" t="inlineStr">
+        <is>
+          <t>-44.149185653337554,168.25507426836757</t>
+        </is>
+      </c>
+      <c r="V376" t="inlineStr">
+        <is>
+          <t>-44.148573741557286,168.25528254594536</t>
+        </is>
+      </c>
+      <c r="W376" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="377">
+      <c r="A377" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-22 22:25:40+00:00</t>
+        </is>
+      </c>
+      <c r="B377" t="inlineStr">
+        <is>
+          <t>-44.157667192190196,168.24381190311004</t>
+        </is>
+      </c>
+      <c r="C377" t="inlineStr">
+        <is>
+          <t>-44.157634160015824,168.24478515674514</t>
+        </is>
+      </c>
+      <c r="D377" t="inlineStr">
+        <is>
+          <t>-44.157349877162076,168.24559059932585</t>
+        </is>
+      </c>
+      <c r="E377" t="inlineStr">
+        <is>
+          <t>-44.15699380636385,168.24633643372374</t>
+        </is>
+      </c>
+      <c r="F377" t="inlineStr">
+        <is>
+          <t>-44.15661437179654,168.24702281515368</t>
+        </is>
+      </c>
+      <c r="G377" t="inlineStr">
+        <is>
+          <t>-44.1561642835073,168.24764333847241</t>
+        </is>
+      </c>
+      <c r="H377" t="inlineStr">
+        <is>
+          <t>-44.15574160958848,168.24832150760557</t>
+        </is>
+      </c>
+      <c r="I377" t="inlineStr">
+        <is>
+          <t>-44.15533162057728,168.24901381672967</t>
+        </is>
+      </c>
+      <c r="J377" t="inlineStr">
+        <is>
+          <t>-44.154903893451525,168.2496863611203</t>
+        </is>
+      </c>
+      <c r="K377" t="inlineStr">
+        <is>
+          <t>-44.1544807154247,168.2503429613775</t>
+        </is>
+      </c>
+      <c r="L377" t="inlineStr">
+        <is>
+          <t>-44.15405537482026,168.2509514337824</t>
+        </is>
+      </c>
+      <c r="M377" t="inlineStr">
+        <is>
+          <t>-44.15356449226584,168.2514924679169</t>
+        </is>
+      </c>
+      <c r="N377" t="inlineStr">
+        <is>
+          <t>-44.153052099466585,168.25203623302227</t>
+        </is>
+      </c>
+      <c r="O377" t="inlineStr">
+        <is>
+          <t>-44.15255198815585,168.2526021481577</t>
+        </is>
+      </c>
+      <c r="P377" t="inlineStr">
+        <is>
+          <t>-44.15203804984121,168.25314314396678</t>
+        </is>
+      </c>
+      <c r="Q377" t="inlineStr">
+        <is>
+          <t>-44.15152011997948,168.25365024749112</t>
+        </is>
+      </c>
+      <c r="R377" t="inlineStr">
+        <is>
+          <t>-44.15097709328853,168.25409242994434</t>
+        </is>
+      </c>
+      <c r="S377" t="inlineStr">
+        <is>
+          <t>-44.150398952538865,168.25448302512703</t>
+        </is>
+      </c>
+      <c r="T377" t="inlineStr">
+        <is>
+          <t>-44.14980011008257,168.25481700100795</t>
+        </is>
+      </c>
+      <c r="U377" t="inlineStr">
+        <is>
+          <t>-44.14918403607658,168.25506817870462</t>
+        </is>
+      </c>
+      <c r="V377" t="inlineStr">
+        <is>
+          <t>-44.14857287257272,168.25527821753926</t>
+        </is>
+      </c>
+      <c r="W377" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0455/nzd0455.xlsx
+++ b/data/nzd0455/nzd0455.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W377"/>
+  <dimension ref="A1:W378"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -28723,6 +28723,81 @@
         <v>355.79</v>
       </c>
       <c r="W377" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="378">
+      <c r="A378" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-07 22:25:39+00:00</t>
+        </is>
+      </c>
+      <c r="B378" t="n">
+        <v>395.89</v>
+      </c>
+      <c r="C378" t="n">
+        <v>359.54</v>
+      </c>
+      <c r="D378" t="n">
+        <v>357.17</v>
+      </c>
+      <c r="E378" t="n">
+        <v>364.02</v>
+      </c>
+      <c r="F378" t="n">
+        <v>368.39</v>
+      </c>
+      <c r="G378" t="n">
+        <v>373.97</v>
+      </c>
+      <c r="H378" t="n">
+        <v>374.8</v>
+      </c>
+      <c r="I378" t="n">
+        <v>373.24</v>
+      </c>
+      <c r="J378" t="n">
+        <v>373.6</v>
+      </c>
+      <c r="K378" t="n">
+        <v>375.47</v>
+      </c>
+      <c r="L378" t="n">
+        <v>372.78</v>
+      </c>
+      <c r="M378" t="n">
+        <v>369.45</v>
+      </c>
+      <c r="N378" t="n">
+        <v>365.9</v>
+      </c>
+      <c r="O378" t="n">
+        <v>362.18</v>
+      </c>
+      <c r="P378" t="n">
+        <v>359.51</v>
+      </c>
+      <c r="Q378" t="n">
+        <v>359.44</v>
+      </c>
+      <c r="R378" t="n">
+        <v>349.38</v>
+      </c>
+      <c r="S378" t="n">
+        <v>352.25</v>
+      </c>
+      <c r="T378" t="n">
+        <v>347.96</v>
+      </c>
+      <c r="U378" t="n">
+        <v>358.71</v>
+      </c>
+      <c r="V378" t="n">
+        <v>358.7</v>
+      </c>
+      <c r="W378" t="inlineStr">
         <is>
           <t>L8</t>
         </is>
@@ -28739,7 +28814,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B389"/>
+  <dimension ref="A1:B390"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -32632,6 +32707,16 @@
       </c>
       <c r="B389" t="n">
         <v>-0.78</v>
+      </c>
+    </row>
+    <row r="390">
+      <c r="A390" t="inlineStr">
+        <is>
+          <t>2026-06-07 22:30:00+00:00</t>
+        </is>
+      </c>
+      <c r="B390" t="n">
+        <v>-0.65</v>
       </c>
     </row>
   </sheetData>
@@ -32800,28 +32885,28 @@
         <v>0.0326</v>
       </c>
       <c r="I2" t="n">
-        <v>0.254094433234254</v>
+        <v>0.2602145534448707</v>
       </c>
       <c r="J2" t="n">
+        <v>377</v>
+      </c>
+      <c r="K2" t="n">
         <v>376</v>
       </c>
-      <c r="K2" t="n">
-        <v>375</v>
-      </c>
       <c r="L2" t="n">
-        <v>0.02867848051963851</v>
+        <v>0.03010740029741121</v>
       </c>
       <c r="M2" t="n">
-        <v>7.787643673909209</v>
+        <v>7.793657635379899</v>
       </c>
       <c r="N2" t="n">
-        <v>118.1845447346035</v>
+        <v>118.2335315343738</v>
       </c>
       <c r="O2" t="n">
-        <v>10.87127153255789</v>
+        <v>10.8735243382435</v>
       </c>
       <c r="P2" t="n">
-        <v>377.3339265396745</v>
+        <v>377.2659759203661</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -32878,28 +32963,28 @@
         <v>0.08740000000000001</v>
       </c>
       <c r="I3" t="n">
-        <v>0.4653653765504301</v>
+        <v>0.4683183567848612</v>
       </c>
       <c r="J3" t="n">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="K3" t="n">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="L3" t="n">
-        <v>0.2603079581165448</v>
+        <v>0.2633370561735384</v>
       </c>
       <c r="M3" t="n">
-        <v>4.430813503639088</v>
+        <v>4.434951579979707</v>
       </c>
       <c r="N3" t="n">
-        <v>33.37196700271718</v>
+        <v>33.36835783329539</v>
       </c>
       <c r="O3" t="n">
-        <v>5.776847496924008</v>
+        <v>5.776535106211629</v>
       </c>
       <c r="P3" t="n">
-        <v>341.3701383099713</v>
+        <v>341.3374481959593</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -32956,28 +33041,28 @@
         <v>0.07199999999999999</v>
       </c>
       <c r="I4" t="n">
-        <v>0.7287329428560304</v>
+        <v>0.7300381567086365</v>
       </c>
       <c r="J4" t="n">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="K4" t="n">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="L4" t="n">
-        <v>0.4350685573169162</v>
+        <v>0.4372090853350905</v>
       </c>
       <c r="M4" t="n">
-        <v>4.762808181830978</v>
+        <v>4.75710873348378</v>
       </c>
       <c r="N4" t="n">
-        <v>37.39426681663216</v>
+        <v>37.31166617495717</v>
       </c>
       <c r="O4" t="n">
-        <v>6.115085184740451</v>
+        <v>6.108327608679578</v>
       </c>
       <c r="P4" t="n">
-        <v>335.1050902246771</v>
+        <v>335.0906412320443</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -33034,28 +33119,28 @@
         <v>0.0653</v>
       </c>
       <c r="I5" t="n">
-        <v>0.7473596715749377</v>
+        <v>0.7485303472519866</v>
       </c>
       <c r="J5" t="n">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="K5" t="n">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="L5" t="n">
-        <v>0.4997498527100807</v>
+        <v>0.5018146024040783</v>
       </c>
       <c r="M5" t="n">
-        <v>4.201838639943946</v>
+        <v>4.197082047931558</v>
       </c>
       <c r="N5" t="n">
-        <v>30.31963972942805</v>
+        <v>30.25256114761522</v>
       </c>
       <c r="O5" t="n">
-        <v>5.50632724503621</v>
+        <v>5.50023282667336</v>
       </c>
       <c r="P5" t="n">
-        <v>341.7116525966647</v>
+        <v>341.6986929700111</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -33112,28 +33197,28 @@
         <v>0.07149999999999999</v>
       </c>
       <c r="I6" t="n">
-        <v>0.7910856635560165</v>
+        <v>0.791425673346508</v>
       </c>
       <c r="J6" t="n">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="K6" t="n">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="L6" t="n">
-        <v>0.4723725518330864</v>
+        <v>0.4739678205920473</v>
       </c>
       <c r="M6" t="n">
-        <v>4.527331668507967</v>
+        <v>4.51719165223773</v>
       </c>
       <c r="N6" t="n">
-        <v>37.90704425469941</v>
+        <v>37.80762076879954</v>
       </c>
       <c r="O6" t="n">
-        <v>6.156869679853505</v>
+        <v>6.148790187410816</v>
       </c>
       <c r="P6" t="n">
-        <v>346.509042646</v>
+        <v>346.5052786659073</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -33190,28 +33275,28 @@
         <v>0.0478</v>
       </c>
       <c r="I7" t="n">
-        <v>0.6339043929338246</v>
+        <v>0.633917655983401</v>
       </c>
       <c r="J7" t="n">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="K7" t="n">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="L7" t="n">
-        <v>0.484684732052944</v>
+        <v>0.486086441256667</v>
       </c>
       <c r="M7" t="n">
-        <v>3.66282142918858</v>
+        <v>3.653186886315267</v>
       </c>
       <c r="N7" t="n">
-        <v>23.16815027947775</v>
+        <v>23.10669801284001</v>
       </c>
       <c r="O7" t="n">
-        <v>4.813330476860877</v>
+        <v>4.806942688740943</v>
       </c>
       <c r="P7" t="n">
-        <v>356.9349842338476</v>
+        <v>356.9348374090914</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -33268,28 +33353,28 @@
         <v>0.07240000000000001</v>
       </c>
       <c r="I8" t="n">
-        <v>0.6414520013195637</v>
+        <v>0.6428296630063369</v>
       </c>
       <c r="J8" t="n">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="K8" t="n">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="L8" t="n">
-        <v>0.4402015654675488</v>
+        <v>0.442471842509105</v>
       </c>
       <c r="M8" t="n">
-        <v>4.084994861543018</v>
+        <v>4.082265671393069</v>
       </c>
       <c r="N8" t="n">
-        <v>28.37517795119939</v>
+        <v>28.3183932575314</v>
       </c>
       <c r="O8" t="n">
-        <v>5.326835641466647</v>
+        <v>5.321502913419422</v>
       </c>
       <c r="P8" t="n">
-        <v>354.9387889719214</v>
+        <v>354.9235379664844</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -33346,28 +33431,28 @@
         <v>0.0708</v>
       </c>
       <c r="I9" t="n">
-        <v>0.7620241969969349</v>
+        <v>0.7646556062313212</v>
       </c>
       <c r="J9" t="n">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="K9" t="n">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="L9" t="n">
-        <v>0.5585528825404928</v>
+        <v>0.5609559694153796</v>
       </c>
       <c r="M9" t="n">
-        <v>3.861334585535377</v>
+        <v>3.865133961493122</v>
       </c>
       <c r="N9" t="n">
-        <v>24.88754623059834</v>
+        <v>24.88895603043274</v>
       </c>
       <c r="O9" t="n">
-        <v>4.9887419486879</v>
+        <v>4.988883244818698</v>
       </c>
       <c r="P9" t="n">
-        <v>347.7304171908328</v>
+        <v>347.7012869356141</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -33424,28 +33509,28 @@
         <v>0.0804</v>
       </c>
       <c r="I10" t="n">
-        <v>0.6413935948429108</v>
+        <v>0.6455427023087118</v>
       </c>
       <c r="J10" t="n">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="K10" t="n">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="L10" t="n">
-        <v>0.4810005355299727</v>
+        <v>0.4838739467073522</v>
       </c>
       <c r="M10" t="n">
-        <v>3.791319896359511</v>
+        <v>3.800796078787387</v>
       </c>
       <c r="N10" t="n">
-        <v>24.07136703698687</v>
+        <v>24.1751467324311</v>
       </c>
       <c r="O10" t="n">
-        <v>4.906257946438086</v>
+        <v>4.916822829066662</v>
       </c>
       <c r="P10" t="n">
-        <v>348.4109338707198</v>
+        <v>348.3650023759797</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -33502,28 +33587,28 @@
         <v>0.0702</v>
       </c>
       <c r="I11" t="n">
-        <v>0.5179787236374518</v>
+        <v>0.5228830905760975</v>
       </c>
       <c r="J11" t="n">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="K11" t="n">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="L11" t="n">
-        <v>0.3970905781170233</v>
+        <v>0.4004094434307114</v>
       </c>
       <c r="M11" t="n">
-        <v>3.586942934424378</v>
+        <v>3.601687896634181</v>
       </c>
       <c r="N11" t="n">
-        <v>22.0910571135828</v>
+        <v>22.26667095228242</v>
       </c>
       <c r="O11" t="n">
-        <v>4.700112457546394</v>
+        <v>4.718757352553999</v>
       </c>
       <c r="P11" t="n">
-        <v>352.1329938797222</v>
+        <v>352.0787015033249</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -33580,28 +33665,28 @@
         <v>0.0683</v>
       </c>
       <c r="I12" t="n">
-        <v>0.764900179989885</v>
+        <v>0.7678725065867206</v>
       </c>
       <c r="J12" t="n">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="K12" t="n">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="L12" t="n">
-        <v>0.581000646350746</v>
+        <v>0.5833270649705786</v>
       </c>
       <c r="M12" t="n">
-        <v>3.758652146634762</v>
+        <v>3.765030793095058</v>
       </c>
       <c r="N12" t="n">
-        <v>22.88107536985089</v>
+        <v>22.90640972274247</v>
       </c>
       <c r="O12" t="n">
-        <v>4.783416704600477</v>
+        <v>4.786064116029211</v>
       </c>
       <c r="P12" t="n">
-        <v>346.5411186242322</v>
+        <v>346.5082143419079</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -33658,28 +33743,28 @@
         <v>0.0834</v>
       </c>
       <c r="I13" t="n">
-        <v>0.7960458821492331</v>
+        <v>0.8001284866358006</v>
       </c>
       <c r="J13" t="n">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="K13" t="n">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="L13" t="n">
-        <v>0.5665375767891314</v>
+        <v>0.5689010706436095</v>
       </c>
       <c r="M13" t="n">
-        <v>4.063883380136056</v>
+        <v>4.073480469723433</v>
       </c>
       <c r="N13" t="n">
-        <v>26.29233166769133</v>
+        <v>26.38488965703166</v>
       </c>
       <c r="O13" t="n">
-        <v>5.127604866571851</v>
+        <v>5.136622397746564</v>
       </c>
       <c r="P13" t="n">
-        <v>340.2331615687226</v>
+        <v>340.1879662759888</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -33736,28 +33821,28 @@
         <v>0.163</v>
       </c>
       <c r="I14" t="n">
-        <v>0.8846939271089149</v>
+        <v>0.8885976095704227</v>
       </c>
       <c r="J14" t="n">
+        <v>377</v>
+      </c>
+      <c r="K14" t="n">
         <v>376</v>
       </c>
-      <c r="K14" t="n">
-        <v>375</v>
-      </c>
       <c r="L14" t="n">
-        <v>0.6140526796689514</v>
+        <v>0.6161406895374748</v>
       </c>
       <c r="M14" t="n">
-        <v>3.916578687396939</v>
+        <v>3.926937169377779</v>
       </c>
       <c r="N14" t="n">
-        <v>26.58716332435675</v>
+        <v>26.66426260852985</v>
       </c>
       <c r="O14" t="n">
-        <v>5.156274170790063</v>
+        <v>5.163745017768582</v>
       </c>
       <c r="P14" t="n">
-        <v>334.6808559607945</v>
+        <v>334.6375140603555</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -33814,28 +33899,28 @@
         <v>0.1423</v>
       </c>
       <c r="I15" t="n">
-        <v>0.7700286804512895</v>
+        <v>0.774189538916196</v>
       </c>
       <c r="J15" t="n">
+        <v>377</v>
+      </c>
+      <c r="K15" t="n">
         <v>376</v>
       </c>
-      <c r="K15" t="n">
-        <v>375</v>
-      </c>
       <c r="L15" t="n">
-        <v>0.5514020918490982</v>
+        <v>0.5538656539615561</v>
       </c>
       <c r="M15" t="n">
-        <v>3.99972771419594</v>
+        <v>4.008990628029198</v>
       </c>
       <c r="N15" t="n">
-        <v>25.89325749979519</v>
+        <v>25.99045677434769</v>
       </c>
       <c r="O15" t="n">
-        <v>5.088541785206759</v>
+        <v>5.098083637441396</v>
       </c>
       <c r="P15" t="n">
-        <v>333.5810466063996</v>
+        <v>333.5346753666605</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -33892,28 +33977,28 @@
         <v>0.0774</v>
       </c>
       <c r="I16" t="n">
-        <v>0.6935779417973434</v>
+        <v>0.6971718586933011</v>
       </c>
       <c r="J16" t="n">
+        <v>377</v>
+      </c>
+      <c r="K16" t="n">
         <v>376</v>
       </c>
-      <c r="K16" t="n">
-        <v>375</v>
-      </c>
       <c r="L16" t="n">
-        <v>0.5142519583112016</v>
+        <v>0.5169625695410888</v>
       </c>
       <c r="M16" t="n">
-        <v>3.867374122524847</v>
+        <v>3.873662255828744</v>
       </c>
       <c r="N16" t="n">
-        <v>24.38988219036006</v>
+        <v>24.44890840814984</v>
       </c>
       <c r="O16" t="n">
-        <v>4.938611362555274</v>
+        <v>4.94458374467961</v>
       </c>
       <c r="P16" t="n">
-        <v>334.0496793925738</v>
+        <v>334.0096265084417</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -33970,28 +34055,28 @@
         <v>0.1178</v>
       </c>
       <c r="I17" t="n">
-        <v>0.8283261993614435</v>
+        <v>0.830894754836537</v>
       </c>
       <c r="J17" t="n">
+        <v>377</v>
+      </c>
+      <c r="K17" t="n">
         <v>376</v>
       </c>
-      <c r="K17" t="n">
-        <v>375</v>
-      </c>
       <c r="L17" t="n">
-        <v>0.6233414005754827</v>
+        <v>0.6254384676548554</v>
       </c>
       <c r="M17" t="n">
-        <v>3.885558334693678</v>
+        <v>3.887342029083664</v>
       </c>
       <c r="N17" t="n">
-        <v>22.25403485194393</v>
+        <v>22.25813177683208</v>
       </c>
       <c r="O17" t="n">
-        <v>4.71741824009107</v>
+        <v>4.717852453906553</v>
       </c>
       <c r="P17" t="n">
-        <v>332.3145857194327</v>
+        <v>332.285960111827</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -34048,28 +34133,28 @@
         <v>0.1043</v>
       </c>
       <c r="I18" t="n">
-        <v>0.8629169279804717</v>
+        <v>0.8633156891214685</v>
       </c>
       <c r="J18" t="n">
+        <v>377</v>
+      </c>
+      <c r="K18" t="n">
         <v>376</v>
       </c>
-      <c r="K18" t="n">
-        <v>375</v>
-      </c>
       <c r="L18" t="n">
-        <v>0.6380228622221494</v>
+        <v>0.6395119093721644</v>
       </c>
       <c r="M18" t="n">
-        <v>3.877125919459257</v>
+        <v>3.868663324836334</v>
       </c>
       <c r="N18" t="n">
-        <v>22.6760252111027</v>
+        <v>22.61724186611479</v>
       </c>
       <c r="O18" t="n">
-        <v>4.761935028021981</v>
+        <v>4.755758810759309</v>
       </c>
       <c r="P18" t="n">
-        <v>325.4655949674753</v>
+        <v>325.4611509209825</v>
       </c>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr">
@@ -34126,28 +34211,28 @@
         <v>0.1026</v>
       </c>
       <c r="I19" t="n">
-        <v>1.000381392059223</v>
+        <v>1.003434553180453</v>
       </c>
       <c r="J19" t="n">
+        <v>377</v>
+      </c>
+      <c r="K19" t="n">
         <v>376</v>
       </c>
-      <c r="K19" t="n">
-        <v>375</v>
-      </c>
       <c r="L19" t="n">
-        <v>0.7399169446600682</v>
+        <v>0.7412530343760747</v>
       </c>
       <c r="M19" t="n">
-        <v>3.55012322487802</v>
+        <v>3.556110817835802</v>
       </c>
       <c r="N19" t="n">
-        <v>18.88184152258777</v>
+        <v>18.92103875891987</v>
       </c>
       <c r="O19" t="n">
-        <v>4.345324098682142</v>
+        <v>4.349832038012488</v>
       </c>
       <c r="P19" t="n">
-        <v>319.5887797341872</v>
+        <v>319.5547533746009</v>
       </c>
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr">
@@ -34204,28 +34289,28 @@
         <v>0.1406</v>
       </c>
       <c r="I20" t="n">
-        <v>0.9645382368063357</v>
+        <v>0.9639915565863505</v>
       </c>
       <c r="J20" t="n">
+        <v>377</v>
+      </c>
+      <c r="K20" t="n">
         <v>376</v>
       </c>
-      <c r="K20" t="n">
-        <v>375</v>
-      </c>
       <c r="L20" t="n">
-        <v>0.6555607987031802</v>
+        <v>0.6565431046654439</v>
       </c>
       <c r="M20" t="n">
-        <v>4.144952244656395</v>
+        <v>4.136161313689817</v>
       </c>
       <c r="N20" t="n">
-        <v>26.2375058683355</v>
+        <v>26.17059193410717</v>
       </c>
       <c r="O20" t="n">
-        <v>5.122255935458077</v>
+        <v>5.115720079725548</v>
       </c>
       <c r="P20" t="n">
-        <v>323.1180347396297</v>
+        <v>323.1241272899424</v>
       </c>
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr">
@@ -34282,28 +34367,28 @@
         <v>0.1091</v>
       </c>
       <c r="I21" t="n">
-        <v>0.8872249940649799</v>
+        <v>0.8881877442694535</v>
       </c>
       <c r="J21" t="n">
+        <v>377</v>
+      </c>
+      <c r="K21" t="n">
         <v>376</v>
       </c>
-      <c r="K21" t="n">
-        <v>375</v>
-      </c>
       <c r="L21" t="n">
-        <v>0.5935980441016777</v>
+        <v>0.5953958612869017</v>
       </c>
       <c r="M21" t="n">
-        <v>4.319451090737774</v>
+        <v>4.312773286512043</v>
       </c>
       <c r="N21" t="n">
-        <v>28.92776741401728</v>
+        <v>28.85972259782185</v>
       </c>
       <c r="O21" t="n">
-        <v>5.378453998503407</v>
+        <v>5.372124588821619</v>
       </c>
       <c r="P21" t="n">
-        <v>333.0675618457884</v>
+        <v>333.0568323482779</v>
       </c>
       <c r="Q21" t="inlineStr"/>
       <c r="R21" t="inlineStr">
@@ -34360,28 +34445,28 @@
         <v>0.1106</v>
       </c>
       <c r="I22" t="n">
-        <v>0.8190313967062008</v>
+        <v>0.8214817444580426</v>
       </c>
       <c r="J22" t="n">
+        <v>377</v>
+      </c>
+      <c r="K22" t="n">
         <v>376</v>
       </c>
-      <c r="K22" t="n">
-        <v>375</v>
-      </c>
       <c r="L22" t="n">
-        <v>0.4937108348450353</v>
+        <v>0.4962127262553581</v>
       </c>
       <c r="M22" t="n">
-        <v>4.983256128655134</v>
+        <v>4.9815239660876</v>
       </c>
       <c r="N22" t="n">
-        <v>36.9242029094046</v>
+        <v>36.88359273733705</v>
       </c>
       <c r="O22" t="n">
-        <v>6.076528853663463</v>
+        <v>6.073186374329134</v>
       </c>
       <c r="P22" t="n">
-        <v>332.0547491348204</v>
+        <v>332.027440908885</v>
       </c>
       <c r="Q22" t="inlineStr"/>
       <c r="R22" t="inlineStr">
@@ -34419,7 +34504,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W377"/>
+  <dimension ref="A1:W378"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -78491,6 +78576,123 @@
         </is>
       </c>
     </row>
+    <row r="378">
+      <c r="A378" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-07 22:25:39+00:00</t>
+        </is>
+      </c>
+      <c r="B378" t="inlineStr">
+        <is>
+          <t>-44.15762515533886,168.24378382649988</t>
+        </is>
+      </c>
+      <c r="C378" t="inlineStr">
+        <is>
+          <t>-44.157618041896264,168.24477439113778</t>
+        </is>
+      </c>
+      <c r="D378" t="inlineStr">
+        <is>
+          <t>-44.15733570297474,168.24558113198592</t>
+        </is>
+      </c>
+      <c r="E378" t="inlineStr">
+        <is>
+          <t>-44.15698184719931,168.2463275238481</t>
+        </is>
+      </c>
+      <c r="F378" t="inlineStr">
+        <is>
+          <t>-44.15661082761857,168.24701939901456</t>
+        </is>
+      </c>
+      <c r="G378" t="inlineStr">
+        <is>
+          <t>-44.15615790443854,168.24763622942965</t>
+        </is>
+      </c>
+      <c r="H378" t="inlineStr">
+        <is>
+          <t>-44.155729692697136,168.2483082269668</t>
+        </is>
+      </c>
+      <c r="I378" t="inlineStr">
+        <is>
+          <t>-44.155318231657716,168.24899889552347</t>
+        </is>
+      </c>
+      <c r="J378" t="inlineStr">
+        <is>
+          <t>-44.15489330853879,168.24967456476597</t>
+        </is>
+      </c>
+      <c r="K378" t="inlineStr">
+        <is>
+          <t>-44.15446551740564,168.25032443388537</t>
+        </is>
+      </c>
+      <c r="L378" t="inlineStr">
+        <is>
+          <t>-44.154043915126955,168.2509336821824</t>
+        </is>
+      </c>
+      <c r="M378" t="inlineStr">
+        <is>
+          <t>-44.15355127333787,168.2514686364278</t>
+        </is>
+      </c>
+      <c r="N378" t="inlineStr">
+        <is>
+          <t>-44.15304540776845,168.2520241690005</t>
+        </is>
+      </c>
+      <c r="O378" t="inlineStr">
+        <is>
+          <t>-44.15254046973221,168.25258138230257</t>
+        </is>
+      </c>
+      <c r="P378" t="inlineStr">
+        <is>
+          <t>-44.152029767596595,168.2531282123935</t>
+        </is>
+      </c>
+      <c r="Q378" t="inlineStr">
+        <is>
+          <t>-44.15151446532033,168.25363793437293</t>
+        </is>
+      </c>
+      <c r="R378" t="inlineStr">
+        <is>
+          <t>-44.15098659966989,168.25411932138462</t>
+        </is>
+      </c>
+      <c r="S378" t="inlineStr">
+        <is>
+          <t>-44.150381865953555,168.25443183848216</t>
+        </is>
+      </c>
+      <c r="T378" t="inlineStr">
+        <is>
+          <t>-44.14980328544195,168.25482651349395</t>
+        </is>
+      </c>
+      <c r="U378" t="inlineStr">
+        <is>
+          <t>-44.14917750482713,168.25504358583848</t>
+        </is>
+      </c>
+      <c r="V378" t="inlineStr">
+        <is>
+          <t>-44.14856584827486,168.2552432295951</t>
+        </is>
+      </c>
+      <c r="W378" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
